--- a/research/brics_universities/output/BRICS_universities_south_africa.xlsx
+++ b/research/brics_universities/output/BRICS_universities_south_africa.xlsx
@@ -4915,26 +4915,26 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>segun.obadire@univen.ac.za</t>
+          <t>international.students@univen.ac.za</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Dr Olusegun Obadire
-И.о. директора Офиса международных связей
-Управление международных связей и партнёрств (Directorate of International Relations and Partnerships)
+Директор Управления международных связей и партнёрств (Director: International Relations and Partnerships)
+Управление международных связей и партнёрств (IRP Directorate) — общий ящик
 Обращение: Dear Dr Obadire,</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>segun.obadire@univen.ac.za</t>
+          <t>international.students@univen.ac.za</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr"/>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>+27 15 962 8000</t>
+          <t>+27 15 962 9347 / 9348 (IRP); +27 15 962 8000 (коммутатор)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -4983,15 +4983,16 @@
       </c>
       <c r="AE21" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF21" s="4" t="inlineStr">
         <is>
-          <t>• Сайт univen.ac.za недоступен (503) — данные из поисковой выдачи
-• Dr Olusegun Obadire указан как и.о. директора International Relations Office в списке IEASA 2025 — статус на 2026 не подтверждён
-• В выдаче встречаются адреса univenofficial@univen.ac.za и International.admissions@univen.ac.za (не проверены на открытой странице)
-• Быстрая проверка: спутников не найдено</t>
+          <t>• Сайт univen.ac.za напрямую из нашей сети недоступен (ошибка TLS через прокси); страницы открыты через r.jina.ai 04.10.2026
+• Dr Olusegun Obadire — Director: International Relations and Partnerships (страница Director’s Profile). Личный e-mail директора (segun.obadire@univen.ac.za, из IEASA 2025) на сайте не опубликован — заменён на общий international.students@univen.ac.za
+• По вопросам научного сотрудничества и институциональных партнёрств сайт IRP указывает matome.mokoena@univen.ac.za; мобильность/Erasmus+ — nontlanhla.ntakana@univen.ac.za; WhatsApp IRP +27 60 677 0033
+• Быстрая проверка: спутников не найдено
+• Перепроверка: Сайт univen.ac.za открыт через reader-сервис 04.10.2026: VC Prof Bernard Nthambeleni, директор IRP Dr Olusegun Obadire (уже не «и.о.»), общий e-mail и телефоны IRP, адрес Private Bag X5050 подтверждены; e-mail international заменён на официальный общий ящик IRP</t>
         </is>
       </c>
       <c r="AG21" s="4" t="inlineStr">
@@ -6257,14 +6258,16 @@
       </c>
       <c r="AE30" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>• Общий email и международный офис на сайте не опубликованы; studentrecruitment@spu.ac.za — ящик набора студентов (единственный общий адрес) — лучше звонить на коммутатор +27 53 491 0000 и запросить адрес офиса ректора
 • Молодой университет (осн. 2014) в Кимберли; для исследовательского партнёрства релевантен DVC: Research, Innovation and Postgraduate Affairs Prof. Jose Frantz
-• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки</t>
+• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки
+• 04.10.2026 на сайте подтверждены: VC Prof. Debra Meyer (Executive Management), коммутатор +27 53 491 0000 и адрес Central Campus (страница Contact); общего e-mail и международного офиса на сайте по-прежнему нет
+• Перепроверка: Ректор, телефон и адрес подтверждены на сайте spu.ac.za 04.10.2026; общий e-mail/международный офис не опубликованы</t>
         </is>
       </c>
       <c r="AG30" s="4" t="inlineStr">
@@ -6831,7 +6834,9 @@
 • Prof Kunene назначена ректором с 2026 г. (Prof Mtose оставалась до 31.03.2026) — проверить вступление в должность
 • Общего e-mail не найдено; admissions@unizulu.ac.za — адрес приёмной комиссии
 • Международный офис и его руководитель не установлены; в IEASA 2025 университет представляла Prof Nontokozo Mashiya (Director: VC's Office, MashiyaN@unizulu.ac.za)
-• Быстрая проверка: спутников не найдено</t>
+• Быстрая проверка: спутников не найдено
+• Повторная проверка 04.10.2026: официальных страниц международного офиса найти не удалось
+• Перепроверка: Сайт unizulu.ac.za недоступен по HTTPS, по HTTP — заглушка обновления LMS; данные не изменены</t>
         </is>
       </c>
       <c r="AG34" s="4" t="inlineStr">

--- a/research/brics_universities/output/BRICS_universities_south_africa.xlsx
+++ b/research/brics_universities/output/BRICS_universities_south_africa.xlsx
@@ -12,8 +12,8 @@
     <sheet name="ЮАР" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AI$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ЮАР'!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ЮАР'!$A$1:$AJ$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата формирования: 2026-10-04</t>
+          <t>Дата формирования: 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -658,30 +658,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -742,120 +743,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -925,93 +931,98 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
           <t>interoff@sun.ac.za</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>info@sun.ac.za</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+27 21 808 9111</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://www.su.ac.za</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Prof. Deresh Ramjugernath</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Rector and Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>QS2027: 296</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>THE2027: 326–350</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• SUNSAT (1999)
 • SumbandilaSat (2009)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• Dock-Sat (1U target + 2U, docking demonstration CubeSats
 • Not launched)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr"/>
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Electronic Systems Laboratory (ESL), Department of Electrical and Electronic Engineering</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• CSIR (SumbandilaSat operations)
 • SunSpace (spin-off, SumbandilaSat builder)
 • NASA (SUNSAT experiments)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Сайт su.ac.za закрыт Cloudflare (403) — контакты взяты из сниппетов поиска официальных страниц, не открыты напрямую
 • SUNSAT (1999) — первый спутник ЮАР, построен студентами SU; SumbandilaSat (2009) построен SunSpace по контракту с SU, оператор — SU
@@ -1020,7 +1031,7 @@
 • Личный email старшего директора SU International Robert Kotzé: rk@sun.ac.za (подтверждён на сайте IEASA, 2025)</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.ac.za/en/about/governance/rector-and-vice-chancellor
 • Https://www.su.ac.za/en/contact-us
@@ -1032,12 +1043,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1100,39 +1111,44 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>info@cput.ac.za</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+27 21 959 6767</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://www.cput.ac.za</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Prof. Chris Nhlapo</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• ZACUBE-1 / TshepisoSat (2013)
 • ZA-AeroSat (2017, co-built with Stellenbosch University, CPUT radios/antennas)
@@ -1142,45 +1158,45 @@
 • MDASat-1c (2022)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>CPUT satellite ground station, Bellville campus (MDASat-1 operations)</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• French South African Institute of Technology (F'SATI)
 • Africa Space Innovation Centre (ASIC)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Department of Science and Innovation (DSI, MDASat-1 funding ~R20m)
 • SANSA
 • QB50 (von Karman Institute)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Сайт cput.ac.za недоступен (503/таймаут) — данные получены из поисковой выдачи по официальным страницам
 • Лидер ЮАР по CubeSat (F'SATI/ASIC) — приоритетный партнёр для VLEO-группировки
@@ -1189,7 +1205,7 @@
 • ZA-AeroSat (QB50, термосфера 90–320 км) — совместно со Stellenbosch University</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cput.ac.za/about-cput/university-leadership/vice-chancellor
 • Https://iol.co.za/news/2026-03-26-i-am-supposed-to-graduate-next-week-cput-students-demand-vcs-suspension-amid-escalating-protests/
@@ -1201,12 +1217,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1268,52 +1284,57 @@
 Обращение: Dear Mr Mudau,</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>information@sansa.org.za</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+27 12 844 0500</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://www.sansa.org.za</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Mr Humbulani Mudau</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer (CEO)</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>• EOSat-1 (first South African Earth-observation satellite, design &amp; development phase
 • Main contractor Denel Dynamics Spaceteq
 • SA contribution to ARMC constellation)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>SANSA Space Operations, Hartebeesthoek (TT&amp;C; S, C, X, Ku bands; BRICS remote-sensing constellation receiving station); planned deep-space ground complex at Matjiesfontein (MTJ); SANSA Space Science, Hermanus (Space Weather Centre)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>• SANSA Earth Observation
 • SANSA Space Operations (Hartebeesthoek)
@@ -1321,7 +1342,7 @@
 • SANSA Space Engineering (CSIR campus, Pretoria)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• BRICS Remote Sensing Satellite Constellation agreement (2021, with CNSA, ISRO, Roscosmos, AEB/INPE)
 • ARMC constellation (South Africa, Nigeria, Kenya, Algeria)
@@ -1330,26 +1351,26 @@
 • NASA/JPL TT&amp;C heritage</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Космическое агентство ЮАР (не университет) — ключевой национальный партнёр; спутники сами не строит — ZACUBE-1/2 построены CPUT (F'SATI) при участии SANSA, поэтому satellites_launched = 0
 • Отдельного международного офиса/email нет — использован общий ящик головного офиса; CEO Humbulani Mudau с 1 апреля 2023 г
@@ -1357,7 +1378,7 @@
 • Тел.: головной офис +27 12 844 0500; Hartebeesthoek +27 12 334 5000 (spaceops-info@sansa.org.za); Hermanus +27 28 285 0000 (spacesci-info@sansa.org.za)</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sansa.org.za/leadership/
 • Https://www.sansa.org.za/get-in-touch/
@@ -1369,12 +1390,12 @@
 • Https://www.engineeringnews.co.za/article/new-south-african-space-agency-ceo-appointed-2023-03-29</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1440,87 +1461,92 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>Zondon1@ukzn.ac.za</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>enquiries@ukzn.ac.za</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+27 31 260 1111</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://ukzn.ac.za</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Nana Poku</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>QS2027: 600</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Rocket launch gantry at Denel Overberg Test Range, Arniston (built/implemented by ASRI, unveiled 2024; suborbital)</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Aerospace Systems Research Institute (ASRI), School of Engineering — Phoenix hybrid sounding rockets, SAFFIRE orbital liquid rocket engine</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• SANSA (ASRI funding/support
 • SANSA payload flown on ASRI sounding rocket, Dec 2024)
 • Department of Science, Technology and Innovation (DSTI)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="AC5" s="6" t="inlineStr">
+      <c r="AD5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Собственных спутников нет, но ASRI — ведущая в ЮАР группа по ракетным двигателям (суборбитальные ракеты Phoenix, двигатель SAFFIRE для орбитального носителя) — сильный партнёр по запуску
 • Пост директора International Relations, по данным поиска, вакантен; UKZN в форуме директоров международных офисов IEASA (2025) представляет Executive Director: Corporate Relations Dr Normah Zondo (Zondon1@ukzn.ac.za). Оперативный контакт: координатор Global Engagement Nozipho Khumalo, Khumalon9@ukzn.ac.za, +27 31 260 3217; общий ящик CRD: corporaterelations@ukzn.ac.za
@@ -1528,7 +1554,7 @@
 • Обращение: на странице UKZN CRD — «Dr Normah Zondo», на сайте IEASA — «Ms»; использовано Dr</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://ukzn.ac.za/vice-chancellor/
 • Https://ukzn.ac.za/general/
@@ -1542,12 +1568,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1610,71 +1636,76 @@
 Обращение: Dear Ms Maruping,</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>enquiries@sarao.ac.za</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+27 21 506 7300</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://www.sarao.ac.za</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Ms Pontsho Maruping</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
       <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>SARAO Hartebeesthoek site (former HartRAO): 26 m and 15 m radio telescopes (astronomy and geodesy), Satellite Laser Ranger (SLR), GNSS receivers (GPS, GLONASS, Galileo); MeerKAT / SKA-Mid site in the Karoo (Northern Cape)</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>Hartebeesthoek space geodesy (SLR, VLBI, GNSS)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr"/>
       <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AC6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Национальная обсерватория (подразделение NRF), не университет; спутников не строит
 • Станция лазерной локации спутников (SLR) и GNSS в Хартебеестхуке — потенциально полезны для точного определения орбит VLEO-спутников
@@ -1682,7 +1713,7 @@
 • Квота веб-поиска исчерпана — партнёрства с космическими агентствами отдельно не проверялись</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sarao.ac.za/contact/
 • Https://www.sarao.ac.za/about/meet-the-team/
@@ -1690,15 +1721,15 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI6"/>
+  <autoFilter ref="A1:AJ6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1709,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1723,30 +1754,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1807,120 +1839,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -1990,93 +2027,98 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
           <t>interoff@sun.ac.za</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>info@sun.ac.za</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+27 21 808 9111</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://www.su.ac.za</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Prof. Deresh Ramjugernath</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Rector and Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>QS2027: 296</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>THE2027: 326–350</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• SUNSAT (1999)
 • SumbandilaSat (2009)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• Dock-Sat (1U target + 2U, docking demonstration CubeSats
 • Not launched)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr"/>
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Electronic Systems Laboratory (ESL), Department of Electrical and Electronic Engineering</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• CSIR (SumbandilaSat operations)
 • SunSpace (spin-off, SumbandilaSat builder)
 • NASA (SUNSAT experiments)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Сайт su.ac.za закрыт Cloudflare (403) — контакты взяты из сниппетов поиска официальных страниц, не открыты напрямую
 • SUNSAT (1999) — первый спутник ЮАР, построен студентами SU; SumbandilaSat (2009) построен SunSpace по контракту с SU, оператор — SU
@@ -2085,7 +2127,7 @@
 • Личный email старшего директора SU International Robert Kotzé: rk@sun.ac.za (подтверждён на сайте IEASA, 2025)</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.ac.za/en/about/governance/rector-and-vice-chancellor
 • Https://www.su.ac.za/en/contact-us
@@ -2097,12 +2139,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2165,39 +2207,44 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>info@cput.ac.za</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+27 21 959 6767</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://www.cput.ac.za</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Prof. Chris Nhlapo</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• ZACUBE-1 / TshepisoSat (2013)
 • ZA-AeroSat (2017, co-built with Stellenbosch University, CPUT radios/antennas)
@@ -2207,45 +2254,45 @@
 • MDASat-1c (2022)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>CPUT satellite ground station, Bellville campus (MDASat-1 operations)</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• French South African Institute of Technology (F'SATI)
 • Africa Space Innovation Centre (ASIC)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Department of Science and Innovation (DSI, MDASat-1 funding ~R20m)
 • SANSA
 • QB50 (von Karman Institute)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Сайт cput.ac.za недоступен (503/таймаут) — данные получены из поисковой выдачи по официальным страницам
 • Лидер ЮАР по CubeSat (F'SATI/ASIC) — приоритетный партнёр для VLEO-группировки
@@ -2254,7 +2301,7 @@
 • ZA-AeroSat (QB50, термосфера 90–320 км) — совместно со Stellenbosch University</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cput.ac.za/about-cput/university-leadership/vice-chancellor
 • Https://iol.co.za/news/2026-03-26-i-am-supposed-to-graduate-next-week-cput-students-demand-vcs-suspension-amid-escalating-protests/
@@ -2266,12 +2313,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -2333,52 +2380,57 @@
 Обращение: Dear Mr Mudau,</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>information@sansa.org.za</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+27 12 844 0500</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://www.sansa.org.za</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Mr Humbulani Mudau</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer (CEO)</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>• EOSat-1 (first South African Earth-observation satellite, design &amp; development phase
 • Main contractor Denel Dynamics Spaceteq
 • SA contribution to ARMC constellation)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>SANSA Space Operations, Hartebeesthoek (TT&amp;C; S, C, X, Ku bands; BRICS remote-sensing constellation receiving station); planned deep-space ground complex at Matjiesfontein (MTJ); SANSA Space Science, Hermanus (Space Weather Centre)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>• SANSA Earth Observation
 • SANSA Space Operations (Hartebeesthoek)
@@ -2386,7 +2438,7 @@
 • SANSA Space Engineering (CSIR campus, Pretoria)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• BRICS Remote Sensing Satellite Constellation agreement (2021, with CNSA, ISRO, Roscosmos, AEB/INPE)
 • ARMC constellation (South Africa, Nigeria, Kenya, Algeria)
@@ -2395,26 +2447,26 @@
 • NASA/JPL TT&amp;C heritage</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Космическое агентство ЮАР (не университет) — ключевой национальный партнёр; спутники сами не строит — ZACUBE-1/2 построены CPUT (F'SATI) при участии SANSA, поэтому satellites_launched = 0
 • Отдельного международного офиса/email нет — использован общий ящик головного офиса; CEO Humbulani Mudau с 1 апреля 2023 г
@@ -2422,7 +2474,7 @@
 • Тел.: головной офис +27 12 844 0500; Hartebeesthoek +27 12 334 5000 (spaceops-info@sansa.org.za); Hermanus +27 28 285 0000 (spacesci-info@sansa.org.za)</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sansa.org.za/leadership/
 • Https://www.sansa.org.za/get-in-touch/
@@ -2434,12 +2486,12 @@
 • Https://www.engineeringnews.co.za/article/new-south-african-space-agency-ceo-appointed-2023-03-29</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2505,87 +2557,92 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>Zondon1@ukzn.ac.za</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>enquiries@ukzn.ac.za</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+27 31 260 1111</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://ukzn.ac.za</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Nana Poku</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>QS2027: 600</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Rocket launch gantry at Denel Overberg Test Range, Arniston (built/implemented by ASRI, unveiled 2024; suborbital)</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Aerospace Systems Research Institute (ASRI), School of Engineering — Phoenix hybrid sounding rockets, SAFFIRE orbital liquid rocket engine</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• SANSA (ASRI funding/support
 • SANSA payload flown on ASRI sounding rocket, Dec 2024)
 • Department of Science, Technology and Innovation (DSTI)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="AC5" s="6" t="inlineStr">
+      <c r="AD5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Собственных спутников нет, но ASRI — ведущая в ЮАР группа по ракетным двигателям (суборбитальные ракеты Phoenix, двигатель SAFFIRE для орбитального носителя) — сильный партнёр по запуску
 • Пост директора International Relations, по данным поиска, вакантен; UKZN в форуме директоров международных офисов IEASA (2025) представляет Executive Director: Corporate Relations Dr Normah Zondo (Zondon1@ukzn.ac.za). Оперативный контакт: координатор Global Engagement Nozipho Khumalo, Khumalon9@ukzn.ac.za, +27 31 260 3217; общий ящик CRD: corporaterelations@ukzn.ac.za
@@ -2593,7 +2650,7 @@
 • Обращение: на странице UKZN CRD — «Dr Normah Zondo», на сайте IEASA — «Ms»; использовано Dr</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://ukzn.ac.za/vice-chancellor/
 • Https://ukzn.ac.za/general/
@@ -2607,12 +2664,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -2678,79 +2735,84 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>shernice.soobramoney@nwu.ac.za</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>studies@nwu.ac.za</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+27 18 299 1111</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://www.nwu.ac.za</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Prof. Mzubanzi Bismark Tyobeka</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>• Centre for Space Research (CSR
 • Heliospheric physics, astrophysics
 • Neutron monitors, Mahikeng Astronomical Observatory)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>SANSA (training and research collaboration of CSR)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AC6" s="7" t="inlineStr">
+      <c r="AD6" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Общего e-mail нет; studies@nwu.ac.za — адрес для абитуриентов (единственный опубликованный общий)
 • E-mail директора Global Engagement взят из списка Directors Forum IEASA 2025 (личный ящик)
@@ -2758,7 +2820,7 @@
 • Спутников нет, но есть сильный Центр космических исследований (CSR)</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nwu.ac.za/vice-chancellor
 • Https://www.nwu.ac.za/content/nwu-contact-details
@@ -2767,12 +2829,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -2834,79 +2896,84 @@
 Обращение: Dear Prof. Skelton,</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>enquiries@saao.ac.za</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+27 21 447 0025</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>https://www.saao.ac.za</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Prof. Rosalind Skelton</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>Director: SAAO</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>• Sutherland observing station (SALT and other optical telescopes), Northern Cape
 • Instrumentation division</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>IAU Office of Astronomy for Development (IAU OAD, hosted at SAAO)</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AC7" s="7" t="inlineStr">
+      <c r="AD7" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Национальная оптическая обсерватория (подразделение NRF), не университет; спутников не строит
 • Отдельного международного офиса нет — использован общий ящик enquiries@saao.ac.za; Sutherland: +27 23 571 2436
 • Квота веб-поиска исчерпана — космические проекты/партнёрства отдельно не проверялись</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.saao.ac.za/about/
 • Https://www.saao.ac.za/contact/
@@ -2914,12 +2981,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -2982,71 +3049,76 @@
 Обращение: Dear Ms Maruping,</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>enquiries@sarao.ac.za</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+27 21 506 7300</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>https://www.sarao.ac.za</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Ms Pontsho Maruping</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>SARAO Hartebeesthoek site (former HartRAO): 26 m and 15 m radio telescopes (astronomy and geodesy), Satellite Laser Ranger (SLR), GNSS receivers (GPS, GLONASS, Galileo); MeerKAT / SKA-Mid site in the Karoo (Northern Cape)</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>Hartebeesthoek space geodesy (SLR, VLBI, GNSS)</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr"/>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AC8" s="6" t="inlineStr">
+      <c r="AD8" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Национальная обсерватория (подразделение NRF), не университет; спутников не строит
 • Станция лазерной локации спутников (SLR) и GNSS в Хартебеестхуке — потенциально полезны для точного определения орбит VLEO-спутников
@@ -3054,7 +3126,7 @@
 • Квота веб-поиска исчерпана — партнёрства с космическими агентствами отдельно не проверялись</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sarao.ac.za/contact/
 • Https://www.sarao.ac.za/about/meet-the-team/
@@ -3062,12 +3134,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3133,73 +3205,78 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
           <t>iapo@uct.ac.za</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+27 21 650 9111</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>https://www.uct.ac.za</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Prof. Mosa Moshabela</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>QS2027: 184</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>THE2027: =147</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="Z9" s="4" t="inlineStr">
         <is>
           <t>SpaceLab (Department of Electrical Engineering)</t>
         </is>
       </c>
-      <c r="Z9" s="4" t="inlineStr"/>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AC9" s="7" t="inlineStr">
+      <c r="AD9" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Август 2026: ректор Moshabela оспаривает решения Совета университета в Высоком суде — возможна смена руководства, перед отправкой проверить
 • Международный офис (IAPO) возглавляет и.о. директора — почётный профессор Danie Visser
@@ -3207,7 +3284,7 @@
 • Собственных запущенных спутников не найдено; есть SpaceLab (космические технологии)</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uct.ac.za/contact-us
 • Https://uct.ac.za/international/international-staff
@@ -3216,12 +3293,12 @@
 • Https://www.researchgate.net/lab/SpaceLab-Peter-Martinez</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3284,68 +3361,73 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>enquiries@csir.co.za</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+27 12 841 2911</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>https://www.csir.co.za</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Dr. Thulani Dlamini</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="4" t="inlineStr"/>
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>• Defence and Security cluster — Aerospace
 • Centre for High Performance Computing (CHPC)</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="n">
+      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="7" t="inlineStr">
+      <c r="AD10" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Не университет — национальный научный совет (включён намеренно)
 • E-mail и телефон на сайте закодированы скриптом; расшифрованы: enquiries@csir.co.za, +27 12 841 2911
@@ -3353,19 +3435,19 @@
 • Международного офиса нет — писать через общий адрес</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Https://www.csir.co.za/about-us/organisational-structure/our-leadership/group-executive-management
 • Https://www.csir.co.za/connect-and-visit/contact-us
 • Https://en.wikipedia.org/wiki/SumbandilaSat</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3431,76 +3513,81 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
           <t>international@uj.ac.za</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>+27 11 559 4555</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>https://www.uj.ac.za</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Prof. Letlhokwa George Mpedi</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>QS2027: 292</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>THE2027: 351–375</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
       <c r="Y11" s="4" t="inlineStr"/>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="7" t="inlineStr">
+      <c r="AD11" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Сайт uj.ac.za блокирует автоматический доступ (403) — данные из поисковой выдачи
 • Division for Internationalisation: старший директор Prof Ylva Rodny-Gumede (подтверждено списком IEASA 2025); личный e-mail: yrodny-gumede@uj.ac.za
 • Запущенных спутников не найдено</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Https://news.uj.ac.za/news/vice-chancellor-message-24-july-2026/
 • Https://www.uj.ac.za/about/message-from-the-senior-director/
@@ -3509,12 +3596,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -3581,69 +3668,74 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
           <t>isd@up.ac.za</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+27 12 420 3111</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>https://www.up.ac.za</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Prof. Francis Petersen</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>QS2027: 326</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>THE2027: 451–500</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="n">
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="7" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Сайт up.ac.za блокирует автоматический доступ (403) — данные из поисковой выдачи по официальным страницам
 • E-mail isd@up.ac.za (International Cooperation Division) взят из факт-листа/выдачи — желательно перепроверить
@@ -3652,7 +3744,7 @@
 • Глава отдела Mokoduwe подтверждён списком IEASA Directors Forum 2025; личный e-mail: setsipane.mokoduwe@up.ac.za</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.up.ac.za/news/post_3231965-prof-francis-petersen-appointed-as-vice-chancellor-and-principal-of-the-university-of-pretoria
 • Https://www.up.ac.za/vice-chancellor-and-principal
@@ -3661,12 +3753,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -3733,80 +3825,85 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
           <t>Samia.Chasi@wits.ac.za</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>Zeblon.Vilakazi@wits.ac.za</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>+27 11 717 1000</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>https://www.wits.ac.za</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Prof. Zeblon Vilakazi</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>QS2027: 302</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="n">
+      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="7" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Общий email не опубликован; email_general — личный адрес ректора с официальной страницы (тел. +27 11 717 1102)
 • Для партнёрств — Internationalisation and Strategic Partnerships Office (Dr Samia Chasi, с апреля 2025, тел. +27 11 717 9731); International Students Office (Ms Gita Patel, Gita.Patel@wits.ac.za) — студенческая мобильность
 • Собственных запущенных спутников не найдено</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wits.ac.za/about-wits/contact-us/management-contacts/
 • Https://www.wits.ac.za/about-wits/office-of-the-vice-chancellor/
@@ -3817,12 +3914,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -3888,69 +3985,74 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
           <t>internationaloffice@ru.ac.za</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>communications@ru.ac.za</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+27 46 603 8111</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>https://www.ru.ac.za</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Prof. Sizwe Mabizela</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>QS2027: 901-950</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr"/>
       <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="n">
+      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• Общий email не опубликован; communications@ru.ac.za — адрес отдела коммуникаций из футера официального сайта
 • Не путать с Rhodes College (США), у которого есть CubeSat RHOK-SAT
@@ -3958,7 +4060,7 @@
 • Международный офис: тел. +27 46 603 8217; адрес Eden Grove Building, Lucas Avenue, Makhanda 6139</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ru.ac.za/contactus/
 • Https://www.ru.ac.za/internationalisation/contactus/
@@ -3968,12 +4070,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4039,69 +4141,74 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
           <t>trsingh@uwc.ac.za</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>info@uwc.ac.za</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+27 21 959 2911</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>https://www.uwc.ac.za</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Prof. Robert John Balfour</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>Rector and Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr">
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="inlineStr"/>
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="n">
+      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC15" s="7" t="inlineStr">
+      <c r="AD15" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• Ректор Balfour в должности с 1.01.2025 (в UWC должность называется Rector and Vice-Chancellor)
 • Офис международных связей (IRO) также ведёт секретариат SANORD; общий адрес iro@uwc.ac.za встречается в поисковой выдаче, но на официальной странице не подтверждён
@@ -4109,19 +4216,19 @@
 • Сайт ограничивает частоту запросов (429)</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uwc.ac.za/about/leadership
 • Https://www.uwc.ac.za/about/international-relations/contact
 • Https://www.uwc.ac.za/news-and-announcements/news/watch-meet-the-university-of-the-western-capes-new-rector-and-vice-chancellor-prof-robert-balfour-8315</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4187,76 +4294,81 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
           <t>samuelsl@dut.ac.za</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>info@dut.ac.za</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+27 31 373 2000</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>https://www.dut.ac.za</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>Prof. Thandwa Zizwe Mthembu</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="n">
+      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Университет технологий (UoT), ведущий среди шести UoT ЮАР; спутников не найдено (одна проверка)
 • Офис International Education and Partnerships (IEP): ML Sultan Campus, D Block, 7–8 этаж; тел. директора +27 31 373 5474
 • Prof. Mthembu — ректор с октября 2016 г</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>• Https://www.dut.ac.za/contact/
 • Https://www.dut.ac.za/international_education_and_partnerships/
@@ -4265,12 +4377,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4337,69 +4449,74 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
           <t>international@mandela.ac.za</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>info@mandela.ac.za</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+27 41 504 1111</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>https://www.mandela.ac.za</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Prof. Sibongile Muthwa</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="n">
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AD17" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD17" s="4" t="inlineStr">
+      <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• Второй срок ректора Muthwa начался 30.03.2022
 • International Office: старший директор Prof Judy Peter (IEASA 2025), личный e-mail Judy.Peter@mandela.ac.za
@@ -4407,7 +4524,7 @@
 • Адрес international@mandela.ac.za на сайте указан для запросов по учёбе за рубежом</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mandela.ac.za/Leadership-and-Governance
 • Https://www.mandela.ac.za/Research,-Innovation-and-Internationalisation
@@ -4416,12 +4533,12 @@
 • Https://www.universityworldnews.com/post.php?story=20090918125617455</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4486,65 +4603,70 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
           <t>carlien.jooste@smu.ac.za</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+27 12 521 5759</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>https://www.smu.ac.za</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Prof. Dini Mawela</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>Acting Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr">
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr"/>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="n">
+      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC18" s="7" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD18" s="4" t="inlineStr">
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Медицинский университет — профиль слабо соответствует CubeSat-проекту; спутников не найдено
 • Ректор Prof. Tandi Matsha-Erasmus скончалась в июне 2026 г.; обязанности ректора исполняет Prof. Dini Mawela (Acting Vice-Chancellor) — учесть деликатность в письме
@@ -4552,7 +4674,7 @@
 • Международное направление курирует и. о. DVC Prof. Douglas Maleka (Research, Innovation and Internationalisation)</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Https://www.smu.ac.za/contacts/
 • Https://www.smu.ac.za/explore-smu/who-we-are/executive-management/
@@ -4562,12 +4684,12 @@
 • Https://www.timeslive.co.za/news/south-africa/2026-06-18-smu-vice-chancellor-tandi-matsha-erasmus-has-died/</t>
         </is>
       </c>
-      <c r="AH18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr"/>
+      <c r="AI18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4633,76 +4755,81 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
           <t>Internationalisation@tut.ac.za</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>general@tut.ac.za</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+27 86 110 2421</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>https://www.tut.ac.za</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Prof. Tinyiko Maluleke</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="n">
+      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC19" s="7" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Спутников TUT в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки (F'SATI исторически имеет узел в TUT — не проверено)
 • Есть два международных подразделения: Internationalisation Office (партнёрства, Research &amp; Innovation; менеджер Mr Caiphus Motadi, +27 12 382 4731) и International Students Office (internationaloffice@tut.ac.za, студенты)
 • Офис ректора: Elizma van der Linde, +27 12 382 4112, VanDerLindeME@tut.ac.za; в IEASA (2025) TUT представляет Dr Rita Raseleka, Director: Research &amp; Innovation (raselekarm@tut.ac.za)</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tut.ac.za/contact-us
 • Https://www.tut.ac.za/about/executive-management-committee/
@@ -4712,12 +4839,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr"/>
+      <c r="AI19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -4780,65 +4907,70 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
           <t>intpartners@unisa.ac.za</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>enquire@unisa.ac.za</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>https://www.unisa.ac.za</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Prof. Puleng LenkaBula</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="n">
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC20" s="7" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AE20" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Крупнейший в Африке университет дистанционного обучения
 • Ректор LenkaBula переназначена на второй срок с 1.01.2026; вокруг неё были обвинения группы «Save Unisa» — проверить перед отправкой
@@ -4847,7 +4979,7 @@
 • Быстрая проверка: запущенных спутников не найдено</t>
         </is>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.unisa.ac.za/sites/corporate/default/About/Governance-&amp;-management/Executive-management
 • Https://www.unisa.ac.za/sites/corporate/default/About/Internationalisation/Contact-us
@@ -4856,12 +4988,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI20" s="4" t="inlineStr"/>
+      <c r="AI20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -4928,65 +5060,70 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
           <t>international.students@univen.ac.za</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>+27 15 962 9347 / 9348 (IRP); +27 15 962 8000 (коммутатор)</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>https://www.univen.ac.za</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Prof. Bernard Nthambeleni</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="n">
+      <c r="AB21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC21" s="7" t="inlineStr">
+      <c r="AD21" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• Сайт univen.ac.za напрямую из нашей сети недоступен (ошибка TLS через прокси); страницы открыты через r.jina.ai 04.10.2026
 • Dr Olusegun Obadire — Director: International Relations and Partnerships (страница Director’s Profile). Личный e-mail директора (segun.obadire@univen.ac.za, из IEASA 2025) на сайте не опубликован — заменён на общий international.students@univen.ac.za
@@ -4995,7 +5132,7 @@
 • Перепроверка: Сайт univen.ac.za открыт через reader-сервис 04.10.2026: VC Prof Bernard Nthambeleni, директор IRP Dr Olusegun Obadire (уже не «и.о.»), общий e-mail и телефоны IRP, адрес Private Bag X5050 подтверждены; e-mail international заменён на официальный общий ящик IRP</t>
         </is>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.univen.ac.za/news/univen-opens-2026-academic-year-with-a-renewed-commitment-to-excellence-impact-and-student-success/
 • Https://www.univen.ac.za/contact-us/
@@ -5003,12 +5140,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr"/>
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5074,73 +5211,78 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
           <t>jacobsl@ufs.ac.za</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>info@ufs.ac.za</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>+27 51 401 9111</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>https://www.ufs.ac.za</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Prof. Hester C. Klopper</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="S22" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001-1200</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr">
+      <c r="T22" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="n">
+      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC22" s="7" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AE22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Prof. Hester Klopper — ректор с 1 февраля 2025 г., первая женщина на этом посту
 • Международное направление курирует DVC: Strategic Initiatives, International and Institutional Affairs Prof. Sam Tshehla (с 1 апреля 2026)
@@ -5148,7 +5290,7 @@
 • Спутников не найдено (одна проверка)</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ufs.ac.za/contact-us
 • Https://www.ufs.ac.za/international
@@ -5157,12 +5299,12 @@
 • Https://businesstech.co.za/news/lifestyle/864277/south-africa-has-a-new-number-one-university-in-gauteng-second-only-to-uct-nationally/</t>
         </is>
       </c>
-      <c r="AH22" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="inlineStr"/>
+      <c r="AI22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -5226,76 +5368,81 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
           <t>vidok@vut.ac.za</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>vutmedia@vut.ac.za</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>+27 16 950 9000</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>https://www.vut.ac.za</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Prof. Khehla Ndlovu</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="R23" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="inlineStr">
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="n">
+      <c r="AB23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC23" s="7" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD23" s="4" t="inlineStr">
+      <c r="AE23" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• Отдельного общего email нет; vutmedia@vut.ac.za — ящик, привязанный к блоку General Enquiries / медиа на странице контактов
 • Директор International Office Mr Vido Kungune: тел. 016 950 9377, офис A009-18 (подтверждено также IEASA 2025)
 • Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Https://www.vut.ac.za/contact-us/
 • Https://www.vut.ac.za/international-office/
@@ -5304,12 +5451,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -5374,67 +5521,72 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>enquiries@wsu.ac.za</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>+27 47 502 2100</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>https://www.wsu.ac.za</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Dr. Thandi Mgwebi</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="4" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="n">
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="n">
+      <c r="AB24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC24" s="7" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD24" s="4" t="inlineStr">
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• Во входном списке указано как «iYunivesithi Walter Sisulu» — это официальное брендовое название; английское — Walter Sisulu University
 • Директор по интернационализации и партнёрствам — Dr Mzolisi Payi (отдельный e-mail не опубликован); рекомендуется адресовать письмо ему через enquiries@wsu.ac.za
@@ -5442,19 +5594,19 @@
 • Быстрая проверка: спутников не найдено</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wsu.ac.za/en/home-wsu/governance-leadership-wsu/leadership
 • Https://www.wsu.ac.za/en/contact-us
 • Https://www.wsu.ac.za/en/internationalisation-partnerships-directorate</t>
         </is>
       </c>
-      <c r="AH24" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -5516,59 +5668,64 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>info@aims.ac.za</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>https://aims.ac.za</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Karin-Therese Howell</t>
         </is>
       </c>
-      <c r="Q25" s="4" t="inlineStr">
+      <c r="R25" s="4" t="inlineStr">
         <is>
           <t>Executive Director</t>
         </is>
       </c>
-      <c r="R25" s="4" t="inlineStr"/>
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="n">
+      <c r="AB25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" s="7" t="inlineStr">
+      <c r="AD25" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD25" s="4" t="inlineStr">
+      <c r="AE25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Некоммерческий институт (часть панафриканской сети AIMS), а не университет — ownership «Частный» условно
 • Учёное звание руководителя на сайте не указано — в обращении не использовать «Prof.» без проверки
@@ -5576,18 +5733,18 @@
 • Спутниковой деятельности нет; интерес — AI/данные для обработки спутниковых данных</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Https://aims.ac.za/contact/
 • Https://aims.ac.za/team/</t>
         </is>
       </c>
-      <c r="AH25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI25" s="4" t="inlineStr"/>
+      <c r="AI25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -5652,61 +5809,66 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
           <t>vmdwayi@cut.ac.za</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>+27 51 507 3911</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>https://www.cut.ac.za</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>Prof. Pamela Zibuyile Dube</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
+      <c r="R26" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="n">
+      <c r="AB26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" s="7" t="inlineStr">
+      <c r="AD26" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• Университет технологий; общего e-mail нет (только портал Ask CUT)
 • Centre for Global Engagement (CGE): старший директор Valindawo Dwayi (учёное звание/обращение не указано)
@@ -5714,7 +5876,7 @@
 • Быстрая проверка: спутников не найдено</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cut.ac.za/
 • Https://www.cut.ac.za/management
@@ -5722,12 +5884,12 @@
 • Https://www.cut.ac.za/contact-details-by-category</t>
         </is>
       </c>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr"/>
+      <c r="AI26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -5790,82 +5952,87 @@
 Обращение: Dear Mr Lubbe,</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>ruimsig@emeris.ac.za</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>+27 11 950 4000</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>https://www.emeris.ac.za</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Andre Lubbe</t>
         </is>
       </c>
-      <c r="Q27" s="4" t="inlineStr">
+      <c r="R27" s="4" t="inlineStr">
         <is>
           <t>Campus Head (Ruimsig Johannesburg)</t>
         </is>
       </c>
-      <c r="R27" s="4" t="inlineStr"/>
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="n">
+      <c r="AB27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC27" s="7" t="inlineStr">
+      <c r="AD27" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD27" s="4" t="inlineStr">
+      <c r="AE27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• IIE MSA (бывший Monash South Africa) больше не существует как отдельный бренд: сайт iiemsa.co.za перенаправляет на Emeris — объединённый бренд IIE (Varsity College, IIE MSA, Vega, School of Hospitality); частный вуз, регистрация DHET 2007/HE07/002
 • Нет ректора/вице-канцлера и международного офиса на уровне кампуса; указан руководитель кампуса Ruimsig (учёное звание не указано); ruimsig@emeris.ac.za — общий ящик кампуса
 • Частный вуз без инженерно-космического профиля; спутников нет; низкий приоритет для CubeSat-группировки</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• Https://www.emeris.ac.za/campuses/ruimsig-johannesburg
 • Https://www.emeris.ac.za/about
 • Https://www.iiemsa.co.za/ (redirects to emeris.ac.za)</t>
         </is>
       </c>
-      <c r="AH27" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="inlineStr"/>
+      <c r="AI27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -5928,70 +6095,75 @@
 Обращение: Dear Senior Director Mkhize,</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>info@mut.ac.za</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>+27 31 907 7111</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>https://www.mut.ac.za</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Prof. Rushiella Songca</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>Interim Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr"/>
       <c r="S28" s="4" t="inlineStr"/>
       <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="n">
+      <c r="AB28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" s="7" t="inlineStr">
+      <c r="AD28" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD28" s="4" t="inlineStr">
+      <c r="AE28" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• Отдельного международного офиса/email нет: интернационализация находится в директорате Marketing and Communications под кураторством ректора; ведущее лицо — Senior Director: Marketing and Communication (на сайте указан как «M Mkhize», учёное звание не указано)
 • Ректор — временный (Interim VC) Prof. Rushiella Songca; офис ректора: тел. 031 907 7219, adsecretary@mut.ac.za
 • Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mut.ac.za/contact-us/
 • Https://www.mut.ac.za/about-mut/leadership-and-governance/
@@ -5999,12 +6171,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH28" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="inlineStr"/>
+      <c r="AI28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6068,63 +6240,68 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>hello@stadio.ac.za</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>+27 87 158 5000</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>https://www.stadio.ac.za</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Dr. Stanislaus Alexander du Plessis</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="R29" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer (CEO) - Principal</t>
         </is>
       </c>
-      <c r="R29" s="4" t="inlineStr"/>
       <c r="S29" s="4" t="inlineStr"/>
       <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="n">
+      <c r="U29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="n">
+      <c r="AB29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC29" s="7" t="inlineStr">
+      <c r="AD29" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr">
+      <c r="AE29" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>• Частный вуз (STADIO (Pty) Ltd, регистрация DHET 2008/HE07/004), в основном дистанционное обучение
 • Hello@stadio.ac.za — адрес поддержки абитуриентов (единственный опубликованный)
@@ -6132,19 +6309,19 @@
 • Космической деятельности нет — низкий приоритет для приглашения</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>• Https://www.stadio.ac.za/about-stadio/leadership
 • Https://www.stadio.ac.za/contact-us
 • Https://stadio.co.za/contact-us/</t>
         </is>
       </c>
-      <c r="AH29" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="inlineStr"/>
+      <c r="AI29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6205,63 +6382,68 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>studentrecruitment@spu.ac.za</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>+27 53 491 0000</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>https://www.spu.ac.za</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Prof. Debra Meyer</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
+      <c r="R30" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R30" s="4" t="inlineStr"/>
       <c r="S30" s="4" t="inlineStr"/>
       <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="n">
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
-      <c r="AB30" s="4" t="n">
+      <c r="AB30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="7" t="inlineStr">
+      <c r="AD30" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD30" s="4" t="inlineStr">
+      <c r="AE30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>• Общий email и международный офис на сайте не опубликованы; studentrecruitment@spu.ac.za — ящик набора студентов (единственный общий адрес) — лучше звонить на коммутатор +27 53 491 0000 и запросить адрес офиса ректора
 • Молодой университет (осн. 2014) в Кимберли; для исследовательского партнёрства релевантен DVC: Research, Innovation and Postgraduate Affairs Prof. Jose Frantz
@@ -6270,7 +6452,7 @@
 • Перепроверка: Ректор, телефон и адрес подтверждены на сайте spu.ac.za 04.10.2026; общий e-mail/международный офис не опубликованы</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.spu.ac.za/index.php/contact-spu/
 • Https://www.spu.ac.za/index.php/leadership-and-governance/
@@ -6278,12 +6460,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI30" s="4" t="inlineStr"/>
+      <c r="AI30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6349,65 +6531,70 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
           <t>international@ufh.ac.za</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>info@ufh.ac.za</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>+27 40 602 2011</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>https://www.ufh.ac.za</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Prof. Sakhela Buhlungu</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="inlineStr">
+      <c r="R31" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr"/>
       <c r="S31" s="4" t="inlineStr"/>
       <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="n">
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="n">
+      <c r="AB31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC31" s="7" t="inlineStr">
+      <c r="AD31" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD31" s="4" t="inlineStr">
+      <c r="AE31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>• Указан физический адрес кампуса Элис (почтовый ящик на проверенной странице не найден)
 • Директор IAP Mr Lebethe Malefo, личный e-mail LMalefo@ufh.ac.za, тел. +27 43 704 7666; менеджер по партнёрствам Ms Quinter Onyango (QOnyango@ufh.ac.za)
@@ -6415,19 +6602,19 @@
 • Быстрая проверка: спутников не найдено</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ufh.ac.za/about-us
 • Https://www.ufh.ac.za/international-affairs-and-partnerships
 • Https://www.ufh.ac.za/international-affairs-and-partnerships/about-iap</t>
         </is>
       </c>
-      <c r="AH31" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr"/>
+      <c r="AI31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -6491,65 +6678,70 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
           <t>internationaloffice@ul.ac.za</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>enrolment@ul.ac.za</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>+27 15 268 9111</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>https://www.ul.ac.za</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Dr Jeffrey Mabelebele</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="R32" s="4" t="inlineStr"/>
       <c r="S32" s="4" t="inlineStr"/>
       <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="n">
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="n">
+      <c r="AB32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC32" s="7" t="inlineStr">
+      <c r="AD32" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD32" s="4" t="inlineStr">
+      <c r="AE32" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>• Общего email нет — enrolment@ul.ac.za (приём/общие контакты, +27 15 268 3332) указан на сайте как «General contacts»
 • Ректор Dr Jeffrey Mabelebele — назван на сайте «новым» ректором; учёное звание — Dr (не Prof.)
@@ -6557,7 +6749,7 @@
 • Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ul.ac.za/contact-us/
 • Https://www.ul.ac.za/about-us/
@@ -6567,12 +6759,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI32" s="4" t="inlineStr"/>
+      <c r="AI32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -6635,81 +6827,86 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>info@ump.ac.za</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>+27 13 002 0001</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>https://www.ump.ac.za</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Prof. Thenjiwe Meyiwa</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr"/>
       <c r="S33" s="4" t="inlineStr"/>
       <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="n">
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="n">
+      <c r="AB33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="7" t="inlineStr">
+      <c r="AD33" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD33" s="4" t="inlineStr">
+      <c r="AE33" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Молодой университет (основан в 2014 г.), сильный аграрный профиль
 • Директор International Partnerships &amp; Networks — Mr Thabo Dikgale (с 1.03.2026), e-mail не опубликован; рекомендуется адресовать письмо ему через info@ump.ac.za
 • Быстрая проверка: спутников не найдено</t>
         </is>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ump.ac.za/
 • Https://www.ump.ac.za/Research-and-Innovation/Partnerships-(1).aspx</t>
         </is>
       </c>
-      <c r="AH33" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="inlineStr"/>
+      <c r="AI33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -6772,63 +6969,68 @@
 Обращение: Dear Director of the International Office,</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>admissions@unizulu.ac.za</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>+27 35 902 6000</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>https://www.unizulu.ac.za</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Prof. Nokuthula Winfred Kunene</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr"/>
       <c r="S34" s="4" t="inlineStr"/>
       <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="n">
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
-      <c r="AB34" s="4" t="n">
+      <c r="AB34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC34" s="7" t="inlineStr">
+      <c r="AD34" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AE34" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>• Сайт unizulu.ac.za недоступен (503/таймаут) — данные из поисковой выдачи
 • Prof Kunene назначена ректором с 2026 г. (Prof Mtose оставалась до 31.03.2026) — проверить вступление в должность
@@ -6839,7 +7041,7 @@
 • Перепроверка: Сайт unizulu.ac.za недоступен по HTTPS, по HTTP — заглушка обновления LMS; данные не изменены</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Https://witness.co.za/news/2025/09/18/unizulu-appoints-professor-kunene-as-its-new-vice-chancellor/
 • Https://usaf.ac.za/universities-south-africa-welcomes-a-new-cohort-of-vice-chancellors-in-2026/
@@ -6847,15 +7049,15 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AH34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr"/>
+      <c r="AI34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI34"/>
+  <autoFilter ref="A1:AJ34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/research/brics_universities/output/BRICS_universities_south_africa.xlsx
+++ b/research/brics_universities/output/BRICS_universities_south_africa.xlsx
@@ -12,8 +12,8 @@
     <sheet name="ЮАР" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ЮАР'!$A$1:$AJ$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AK$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ЮАР'!$A$1:$AK$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -668,21 +668,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -793,75 +794,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -966,7 +972,7 @@
       </c>
       <c r="S2" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 296</t>
+          <t>QS2027: =296</t>
         </is>
       </c>
       <c r="T2" s="4" t="inlineStr">
@@ -974,64 +980,74 @@
           <t>THE2027: 326–350</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• SUNSAT (1999)
 • SumbandilaSat (2009)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>• Dock-Sat (1U target + 2U, docking demonstration CubeSats
 • Not launched)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr"/>
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>Electronic Systems Laboratory (ESL), Department of Electrical and Electronic Engineering</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>• CSIR (SumbandilaSat operations)
 • SunSpace (spin-off, SumbandilaSat builder)
 • NASA (SUNSAT experiments)</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Сайт su.ac.za закрыт Cloudflare (403) — контакты взяты из сниппетов поиска официальных страниц, не открыты напрямую
 • SUNSAT (1999) — первый спутник ЮАР, построен студентами SU; SumbandilaSat (2009) построен SunSpace по контракту с SU, оператор — SU
 • Почтовый адрес изменён: старый Private Bag X1, Matieland 7602 упразднён; email-домен sun.ac.za может мигрировать на su.ac.za
 • Ректор Prof. Deresh Ramjugernath с 1 апреля 2025 г
-• Личный email старшего директора SU International Robert Kotzé: rk@sun.ac.za (подтверждён на сайте IEASA, 2025)</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• Личный email старшего директора SU International Robert Kotzé: rk@sun.ac.za (подтверждён на сайте IEASA, 2025)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.ac.za/en/about/governance/rector-and-vice-chancellor
 • Https://www.su.ac.za/en/contact-us
@@ -1040,15 +1056,18 @@
 • Https://en.wikipedia.org/wiki/SUNSAT
 • Https://en.wikipedia.org/wiki/SumbandilaSat
 • Nanosats.csv
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1142,13 +1161,30 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• ZACUBE-1 / TshepisoSat (2013)
 • ZA-AeroSat (2017, co-built with Stellenbosch University, CPUT radios/antennas)
@@ -1158,54 +1194,55 @@
 • MDASat-1c (2022)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>CPUT satellite ground station, Bellville campus (MDASat-1 operations)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• French South African Institute of Technology (F'SATI)
 • Africa Space Innovation Centre (ASIC)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• Department of Science and Innovation (DSI, MDASat-1 funding ~R20m)
 • SANSA
 • QB50 (von Karman Institute)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Сайт cput.ac.za недоступен (503/таймаут) — данные получены из поисковой выдачи по официальным страницам
 • Лидер ЮАР по CubeSat (F'SATI/ASIC) — приоритетный партнёр для VLEO-группировки
 • Международные связи ведёт Strategic Initiatives, Internationalisation and Partnerships (SIIP): директор Dr Divinia Jithoo, тел. +27 21 959 5650; e-mail на сайте скрыт — рекомендуется адресовать письмо ей
 • В марте 2026 г. студенты требовали отстранения ректора Nhlapo; по состоянию на июль 2026 он оставался в должности
-• ZA-AeroSat (QB50, термосфера 90–320 км) — совместно со Stellenbosch University</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• ZA-AeroSat (QB50, термосфера 90–320 км) — совместно со Stellenbosch University
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cput.ac.za/about-cput/university-leadership/vice-chancellor
 • Https://iol.co.za/news/2026-03-26-i-am-supposed-to-graduate-next-week-cput-students-demand-vcs-suspension-amid-escalating-protests/
@@ -1214,15 +1251,16 @@
 • Https://www.cput.ac.za/newsroom/news/article/4201/maritime-domain-awareness-satellite-mission-launch-imminent
 • Https://www.cput.ac.za/world-space-week
 • Https://amsat-uk.org/2017/04/15/south-african-qb50-cubesats/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr">
+• Nanosats.csv
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1315,26 +1353,43 @@
           <t>Chief Executive Officer (CEO)</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>• EOSat-1 (first South African Earth-observation satellite, design &amp; development phase
 • Main contractor Denel Dynamics Spaceteq
 • SA contribution to ARMC constellation)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>SANSA Space Operations, Hartebeesthoek (TT&amp;C; S, C, X, Ku bands; BRICS remote-sensing constellation receiving station); planned deep-space ground complex at Matjiesfontein (MTJ); SANSA Space Science, Hermanus (Space Weather Centre)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• SANSA Earth Observation
 • SANSA Space Operations (Hartebeesthoek)
@@ -1342,7 +1397,7 @@
 • SANSA Space Engineering (CSIR campus, Pretoria)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>• BRICS Remote Sensing Satellite Constellation agreement (2021, with CNSA, ISRO, Roscosmos, AEB/INPE)
 • ARMC constellation (South Africa, Nigeria, Kenya, Algeria)
@@ -1351,34 +1406,35 @@
 • NASA/JPL TT&amp;C heritage</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AD4" s="6" t="inlineStr">
+      <c r="AE4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Космическое агентство ЮАР (не университет) — ключевой национальный партнёр; спутники сами не строит — ZACUBE-1/2 построены CPUT (F'SATI) при участии SANSA, поэтому satellites_launched = 0
 • Отдельного международного офиса/email нет — использован общий ящик головного офиса; CEO Humbulani Mudau с 1 апреля 2023 г
 • Станция Hartebeesthoek уже является приёмной станцией группировки BRICS — возможна поддержка TT&amp;C для VLEO-кубсатов
-• Тел.: головной офис +27 12 844 0500; Hartebeesthoek +27 12 334 5000 (spaceops-info@sansa.org.za); Hermanus +27 28 285 0000 (spacesci-info@sansa.org.za)</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• Тел.: головной офис +27 12 844 0500; Hartebeesthoek +27 12 334 5000 (spaceops-info@sansa.org.za); Hermanus +27 28 285 0000 (spacesci-info@sansa.org.za)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sansa.org.za/leadership/
 • Https://www.sansa.org.za/get-in-touch/
@@ -1390,12 +1446,12 @@
 • Https://www.engineeringnews.co.za/article/new-south-african-space-agency-ceo-appointed-2023-03-29</t>
         </is>
       </c>
-      <c r="AI4" s="4" t="inlineStr">
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1496,7 +1552,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 600</t>
+          <t>QS2027: =600</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -1504,57 +1560,67 @@
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Rocket launch gantry at Denel Overberg Test Range, Arniston (built/implemented by ASRI, unveiled 2024; suborbital)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Aerospace Systems Research Institute (ASRI), School of Engineering — Phoenix hybrid sounding rockets, SAFFIRE orbital liquid rocket engine</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>• SANSA (ASRI funding/support
 • SANSA payload flown on ASRI sounding rocket, Dec 2024)
 • Department of Science, Technology and Innovation (DSTI)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="AD5" s="6" t="inlineStr">
+      <c r="AE5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Собственных спутников нет, но ASRI — ведущая в ЮАР группа по ракетным двигателям (суборбитальные ракеты Phoenix, двигатель SAFFIRE для орбитального носителя) — сильный партнёр по запуску
 • Пост директора International Relations, по данным поиска, вакантен; UKZN в форуме директоров международных офисов IEASA (2025) представляет Executive Director: Corporate Relations Dr Normah Zondo (Zondon1@ukzn.ac.za). Оперативный контакт: координатор Global Engagement Nozipho Khumalo, Khumalon9@ukzn.ac.za, +27 31 260 3217; общий ящик CRD: corporaterelations@ukzn.ac.za
 • Prof. Nana Poku — ректор с 24.06.2019, указан на текущем официальном сайте; дата продления срока не проверена
-• Обращение: на странице UKZN CRD — «Dr Normah Zondo», на сайте IEASA — «Ms»; использовано Dr</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• Обращение: на странице UKZN CRD — «Dr Normah Zondo», на сайте IEASA — «Ms»; использовано Dr
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://ukzn.ac.za/vice-chancellor/
 • Https://ukzn.ac.za/general/
@@ -1565,15 +1631,18 @@
 • Https://www.sansa.org.za/2024/12/sansa-payload-takes-flight-at-south-africas-new-rocket-gantry/
 • Https://businesstech.co.za/news/lifestyle/864277/south-africa-has-a-new-number-one-university-in-gauteng-second-only-to-uct-nationally/
 • Https://corporaterelations.ukzn.ac.za/executive-director-3/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1667,53 +1736,71 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>SARAO Hartebeesthoek site (former HartRAO): 26 m and 15 m radio telescopes (astronomy and geodesy), Satellite Laser Ranger (SLR), GNSS receivers (GPS, GLONASS, Galileo); MeerKAT / SKA-Mid site in the Karoo (Northern Cape)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>Hartebeesthoek space geodesy (SLR, VLBI, GNSS)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
       <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AD6" s="6" t="inlineStr">
+      <c r="AE6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Национальная обсерватория (подразделение NRF), не университет; спутников не строит
 • Станция лазерной локации спутников (SLR) и GNSS в Хартебеестхуке — потенциально полезны для точного определения орбит VLEO-спутников
 • Ms Pontsho Maruping — Managing Director с 1 октября 2022 г.; отдельного международного офиса/email нет — использован общий ящик enquiries@sarao.ac.za
-• Квота веб-поиска исчерпана — партнёрства с космическими агентствами отдельно не проверялись</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Квота веб-поиска исчерпана — партнёрства с космическими агентствами отдельно не проверялись
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sarao.ac.za/contact/
 • Https://www.sarao.ac.za/about/meet-the-team/
@@ -1721,15 +1808,15 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI6" s="4" t="inlineStr">
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ6"/>
+  <autoFilter ref="A1:AK6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1740,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1764,21 +1851,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1889,75 +1977,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -2062,7 +2155,7 @@
       </c>
       <c r="S2" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 296</t>
+          <t>QS2027: =296</t>
         </is>
       </c>
       <c r="T2" s="4" t="inlineStr">
@@ -2070,64 +2163,74 @@
           <t>THE2027: 326–350</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• SUNSAT (1999)
 • SumbandilaSat (2009)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>• Dock-Sat (1U target + 2U, docking demonstration CubeSats
 • Not launched)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr"/>
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>Electronic Systems Laboratory (ESL), Department of Electrical and Electronic Engineering</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>• CSIR (SumbandilaSat operations)
 • SunSpace (spin-off, SumbandilaSat builder)
 • NASA (SUNSAT experiments)</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Сайт su.ac.za закрыт Cloudflare (403) — контакты взяты из сниппетов поиска официальных страниц, не открыты напрямую
 • SUNSAT (1999) — первый спутник ЮАР, построен студентами SU; SumbandilaSat (2009) построен SunSpace по контракту с SU, оператор — SU
 • Почтовый адрес изменён: старый Private Bag X1, Matieland 7602 упразднён; email-домен sun.ac.za может мигрировать на su.ac.za
 • Ректор Prof. Deresh Ramjugernath с 1 апреля 2025 г
-• Личный email старшего директора SU International Robert Kotzé: rk@sun.ac.za (подтверждён на сайте IEASA, 2025)</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• Личный email старшего директора SU International Robert Kotzé: rk@sun.ac.za (подтверждён на сайте IEASA, 2025)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.ac.za/en/about/governance/rector-and-vice-chancellor
 • Https://www.su.ac.za/en/contact-us
@@ -2136,15 +2239,18 @@
 • Https://en.wikipedia.org/wiki/SUNSAT
 • Https://en.wikipedia.org/wiki/SumbandilaSat
 • Nanosats.csv
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2238,13 +2344,30 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• ZACUBE-1 / TshepisoSat (2013)
 • ZA-AeroSat (2017, co-built with Stellenbosch University, CPUT radios/antennas)
@@ -2254,54 +2377,55 @@
 • MDASat-1c (2022)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>CPUT satellite ground station, Bellville campus (MDASat-1 operations)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• French South African Institute of Technology (F'SATI)
 • Africa Space Innovation Centre (ASIC)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• Department of Science and Innovation (DSI, MDASat-1 funding ~R20m)
 • SANSA
 • QB50 (von Karman Institute)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Сайт cput.ac.za недоступен (503/таймаут) — данные получены из поисковой выдачи по официальным страницам
 • Лидер ЮАР по CubeSat (F'SATI/ASIC) — приоритетный партнёр для VLEO-группировки
 • Международные связи ведёт Strategic Initiatives, Internationalisation and Partnerships (SIIP): директор Dr Divinia Jithoo, тел. +27 21 959 5650; e-mail на сайте скрыт — рекомендуется адресовать письмо ей
 • В марте 2026 г. студенты требовали отстранения ректора Nhlapo; по состоянию на июль 2026 он оставался в должности
-• ZA-AeroSat (QB50, термосфера 90–320 км) — совместно со Stellenbosch University</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• ZA-AeroSat (QB50, термосфера 90–320 км) — совместно со Stellenbosch University
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cput.ac.za/about-cput/university-leadership/vice-chancellor
 • Https://iol.co.za/news/2026-03-26-i-am-supposed-to-graduate-next-week-cput-students-demand-vcs-suspension-amid-escalating-protests/
@@ -2310,15 +2434,16 @@
 • Https://www.cput.ac.za/newsroom/news/article/4201/maritime-domain-awareness-satellite-mission-launch-imminent
 • Https://www.cput.ac.za/world-space-week
 • Https://amsat-uk.org/2017/04/15/south-african-qb50-cubesats/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr">
+• Nanosats.csv
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -2411,26 +2536,43 @@
           <t>Chief Executive Officer (CEO)</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>• EOSat-1 (first South African Earth-observation satellite, design &amp; development phase
 • Main contractor Denel Dynamics Spaceteq
 • SA contribution to ARMC constellation)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>SANSA Space Operations, Hartebeesthoek (TT&amp;C; S, C, X, Ku bands; BRICS remote-sensing constellation receiving station); planned deep-space ground complex at Matjiesfontein (MTJ); SANSA Space Science, Hermanus (Space Weather Centre)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• SANSA Earth Observation
 • SANSA Space Operations (Hartebeesthoek)
@@ -2438,7 +2580,7 @@
 • SANSA Space Engineering (CSIR campus, Pretoria)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>• BRICS Remote Sensing Satellite Constellation agreement (2021, with CNSA, ISRO, Roscosmos, AEB/INPE)
 • ARMC constellation (South Africa, Nigeria, Kenya, Algeria)
@@ -2447,34 +2589,35 @@
 • NASA/JPL TT&amp;C heritage</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AD4" s="6" t="inlineStr">
+      <c r="AE4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Космическое агентство ЮАР (не университет) — ключевой национальный партнёр; спутники сами не строит — ZACUBE-1/2 построены CPUT (F'SATI) при участии SANSA, поэтому satellites_launched = 0
 • Отдельного международного офиса/email нет — использован общий ящик головного офиса; CEO Humbulani Mudau с 1 апреля 2023 г
 • Станция Hartebeesthoek уже является приёмной станцией группировки BRICS — возможна поддержка TT&amp;C для VLEO-кубсатов
-• Тел.: головной офис +27 12 844 0500; Hartebeesthoek +27 12 334 5000 (spaceops-info@sansa.org.za); Hermanus +27 28 285 0000 (spacesci-info@sansa.org.za)</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• Тел.: головной офис +27 12 844 0500; Hartebeesthoek +27 12 334 5000 (spaceops-info@sansa.org.za); Hermanus +27 28 285 0000 (spacesci-info@sansa.org.za)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sansa.org.za/leadership/
 • Https://www.sansa.org.za/get-in-touch/
@@ -2486,12 +2629,12 @@
 • Https://www.engineeringnews.co.za/article/new-south-african-space-agency-ceo-appointed-2023-03-29</t>
         </is>
       </c>
-      <c r="AI4" s="4" t="inlineStr">
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2592,7 +2735,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 600</t>
+          <t>QS2027: =600</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -2600,57 +2743,67 @@
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Rocket launch gantry at Denel Overberg Test Range, Arniston (built/implemented by ASRI, unveiled 2024; suborbital)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Aerospace Systems Research Institute (ASRI), School of Engineering — Phoenix hybrid sounding rockets, SAFFIRE orbital liquid rocket engine</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>• SANSA (ASRI funding/support
 • SANSA payload flown on ASRI sounding rocket, Dec 2024)
 • Department of Science, Technology and Innovation (DSTI)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="AD5" s="6" t="inlineStr">
+      <c r="AE5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Собственных спутников нет, но ASRI — ведущая в ЮАР группа по ракетным двигателям (суборбитальные ракеты Phoenix, двигатель SAFFIRE для орбитального носителя) — сильный партнёр по запуску
 • Пост директора International Relations, по данным поиска, вакантен; UKZN в форуме директоров международных офисов IEASA (2025) представляет Executive Director: Corporate Relations Dr Normah Zondo (Zondon1@ukzn.ac.za). Оперативный контакт: координатор Global Engagement Nozipho Khumalo, Khumalon9@ukzn.ac.za, +27 31 260 3217; общий ящик CRD: corporaterelations@ukzn.ac.za
 • Prof. Nana Poku — ректор с 24.06.2019, указан на текущем официальном сайте; дата продления срока не проверена
-• Обращение: на странице UKZN CRD — «Dr Normah Zondo», на сайте IEASA — «Ms»; использовано Dr</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• Обращение: на странице UKZN CRD — «Dr Normah Zondo», на сайте IEASA — «Ms»; использовано Dr
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://ukzn.ac.za/vice-chancellor/
 • Https://ukzn.ac.za/general/
@@ -2661,15 +2814,18 @@
 • Https://www.sansa.org.za/2024/12/sansa-payload-takes-flight-at-south-africas-new-rocket-gantry/
 • Https://businesstech.co.za/news/lifestyle/864277/south-africa-has-a-new-number-one-university-in-gauteng-second-only-to-uct-nationally/
 • Https://corporaterelations.ukzn.ac.za/executive-director-3/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -2768,73 +2924,90 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 1001–1200</t>
+        </is>
+      </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr"/>
       <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>• Centre for Space Research (CSR
 • Heliospheric physics, astrophysics
 • Neutron monitors, Mahikeng Astronomical Observatory)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr">
         <is>
           <t>SANSA (training and research collaboration of CSR)</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AD6" s="7" t="inlineStr">
+      <c r="AE6" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Общего e-mail нет; studies@nwu.ac.za — адрес для абитуриентов (единственный опубликованный общий)
 • E-mail директора Global Engagement взят из списка Directors Forum IEASA 2025 (личный ящик)
 • Город — Потчефструм (кампусы также в Махикенге и Вандербейлпарке)
-• Спутников нет, но есть сильный Центр космических исследований (CSR)</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Спутников нет, но есть сильный Центр космических исследований (CSR)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nwu.ac.za/vice-chancellor
 • Https://www.nwu.ac.za/content/nwu-contact-details
 • Https://natural-sciences.nwu.ac.za/space-research
 • Https://www.nwu.ac.za/sites/www.nwu.ac.za/files/files/i-international-students/Presentation-International-Students-web.pdf
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -2927,53 +3100,71 @@
           <t>Director: SAAO</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr"/>
       <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>• Sutherland observing station (SALT and other optical telescopes), Northern Cape
 • Instrumentation division</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>IAU Office of Astronomy for Development (IAU OAD, hosted at SAAO)</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AD7" s="7" t="inlineStr">
+      <c r="AE7" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Национальная оптическая обсерватория (подразделение NRF), не университет; спутников не строит
 • Отдельного международного офиса нет — использован общий ящик enquiries@saao.ac.za; Sutherland: +27 23 571 2436
-• Квота веб-поиска исчерпана — космические проекты/партнёрства отдельно не проверялись</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
+• Квота веб-поиска исчерпана — космические проекты/партнёрства отдельно не проверялись
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.saao.ac.za/about/
 • Https://www.saao.ac.za/contact/
@@ -2981,12 +3172,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI7" s="4" t="inlineStr">
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3080,53 +3271,71 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>SARAO Hartebeesthoek site (former HartRAO): 26 m and 15 m radio telescopes (astronomy and geodesy), Satellite Laser Ranger (SLR), GNSS receivers (GPS, GLONASS, Galileo); MeerKAT / SKA-Mid site in the Karoo (Northern Cape)</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>Hartebeesthoek space geodesy (SLR, VLBI, GNSS)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AD8" s="6" t="inlineStr">
+      <c r="AE8" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Национальная обсерватория (подразделение NRF), не университет; спутников не строит
 • Станция лазерной локации спутников (SLR) и GNSS в Хартебеестхуке — потенциально полезны для точного определения орбит VLEO-спутников
 • Ms Pontsho Maruping — Managing Director с 1 октября 2022 г.; отдельного международного офиса/email нет — использован общий ящик enquiries@sarao.ac.za
-• Квота веб-поиска исчерпана — партнёрства с космическими агентствами отдельно не проверялись</t>
-        </is>
-      </c>
-      <c r="AH8" s="4" t="inlineStr">
+• Квота веб-поиска исчерпана — партнёрства с космическими агентствами отдельно не проверялись
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sarao.ac.za/contact/
 • Https://www.sarao.ac.za/about/meet-the-team/
@@ -3134,12 +3343,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI8" s="4" t="inlineStr">
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3244,61 +3453,74 @@
           <t>THE2027: =147</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>SpaceLab (Department of Electrical Engineering)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
       <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AD9" s="7" t="inlineStr">
+      <c r="AE9" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Август 2026: ректор Moshabela оспаривает решения Совета университета в Высоком суде — возможна смена руководства, перед отправкой проверить
 • Международный офис (IAPO) возглавляет и.о. директора — почётный профессор Danie Visser
 • Партнёрства в IAPO курирует Ms Tracy Goslar (Deputy Director: Internationalisation)
-• Собственных запущенных спутников не найдено; есть SpaceLab (космические технологии)</t>
-        </is>
-      </c>
-      <c r="AH9" s="4" t="inlineStr">
+• Собственных запущенных спутников не найдено; есть SpaceLab (космические технологии)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uct.ac.za/contact-us
 • Https://uct.ac.za/international/international-staff
 • Https://www.news.uct.ac.za/article/-2026-09-17-uct-spring-graduations-vcs-meet-and-greet
 • Https://www.dailymaverick.co.za/article/2026-08-07-another-uct-leadership-crisis-34-complaints-secret-findings-and-a-vc-in-court/
-• Https://www.researchgate.net/lab/SpaceLab-Peter-Martinez</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr">
+• Https://www.researchgate.net/lab/SpaceLab-Peter-Martinez
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3392,62 +3614,80 @@
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>• Defence and Security cluster — Aerospace
 • Centre for High Performance Computing (CHPC)</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="n">
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD10" s="7" t="inlineStr">
+      <c r="AE10" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Не университет — национальный научный совет (включён намеренно)
 • E-mail и телефон на сайте закодированы скриптом; расшифрованы: enquiries@csir.co.za, +27 12 841 2911
 • Исторически CSIR создал Satellite Applications Centre в Хартбистхуке (ныне станция SANSA) и участвовал в программе SumbandilaSat (2009), но собственных спутников не строил
-• Международного офиса нет — писать через общий адрес</t>
-        </is>
-      </c>
-      <c r="AH10" s="4" t="inlineStr">
+• Международного офиса нет — писать через общий адрес
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="inlineStr">
         <is>
           <t>• Https://www.csir.co.za/about-us/organisational-structure/our-leadership/group-executive-management
 • Https://www.csir.co.za/connect-and-visit/contact-us
 • Https://en.wikipedia.org/wiki/SumbandilaSat</t>
         </is>
       </c>
-      <c r="AI10" s="4" t="inlineStr">
+      <c r="AJ10" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3553,41 +3793,43 @@
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="n">
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
       <c r="Y11" s="4" t="inlineStr"/>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
       <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD11" s="7" t="inlineStr">
+      <c r="AE11" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Сайт uj.ac.za блокирует автоматический доступ (403) — данные из поисковой выдачи
 • Division for Internationalisation: старший директор Prof Ylva Rodny-Gumede (подтверждено списком IEASA 2025); личный e-mail: yrodny-gumede@uj.ac.za
-• Запущенных спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr">
+• Запущенных спутников не найдено
+• Ручная проверка: Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
         <is>
           <t>• Https://news.uj.ac.za/news/vice-chancellor-message-24-july-2026/
 • Https://www.uj.ac.za/about/message-from-the-senior-director/
@@ -3596,12 +3838,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AI11" s="4" t="inlineStr">
+      <c r="AJ11" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -3708,43 +3950,45 @@
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
       <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="n">
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD12" s="7" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Сайт up.ac.za блокирует автоматический доступ (403) — данные из поисковой выдачи по официальным страницам
 • E-mail isd@up.ac.za (International Cooperation Division) взят из факт-листа/выдачи — желательно перепроверить
 • Ректор Petersen в должности с 1.10.2024
 • Запущенных спутников не найдено
-• Глава отдела Mokoduwe подтверждён списком IEASA Directors Forum 2025; личный e-mail: setsipane.mokoduwe@up.ac.za</t>
-        </is>
-      </c>
-      <c r="AH12" s="4" t="inlineStr">
+• Глава отдела Mokoduwe подтверждён списком IEASA Directors Forum 2025; личный e-mail: setsipane.mokoduwe@up.ac.za
+• Ручная проверка: Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.up.ac.za/news/post_3231965-prof-francis-petersen-appointed-as-vice-chancellor-and-principal-of-the-university-of-pretoria
 • Https://www.up.ac.za/vice-chancellor-and-principal
@@ -3753,12 +3997,12 @@
 • Https://ieasa.studysa.org/about-us/directors-forum/</t>
         </is>
       </c>
-      <c r="AI12" s="4" t="inlineStr">
+      <c r="AJ12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -3868,42 +4112,52 @@
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="n">
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Общий email не опубликован; email_general — личный адрес ректора с официальной страницы (тел. +27 11 717 1102)
 • Для партнёрств — Internationalisation and Strategic Partnerships Office (Dr Samia Chasi, с апреля 2025, тел. +27 11 717 9731); International Students Office (Ms Gita Patel, Gita.Patel@wits.ac.za) — студенческая мобильность
-• Собственных запущенных спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH13" s="4" t="inlineStr">
+• Собственных запущенных спутников не найдено
+• Рейтинги: QS: в таблице как «University of Witwatersrand»; THE: в таблице как «University of the Witwatersrand»; Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wits.ac.za/about-wits/contact-us/management-contacts/
 • Https://www.wits.ac.za/about-wits/office-of-the-vice-chancellor/
@@ -3911,15 +4165,18 @@
 • Https://www.wits.ac.za/research/staff/
 • Https://www.wits.ac.za/news/latest-news/general-news/2025/2025-11/advancing-meaningful-collaborations-for-wits-.html
 • Https://www.wits.ac.za/internationalstudents/contact-us/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
+      <c r="AK13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4020,62 +4277,78 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 901-950</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
+          <t>QS2027: 901–950</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="n">
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD14" s="7" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• Общий email не опубликован; communications@ru.ac.za — адрес отдела коммуникаций из футера официального сайта
 • Не путать с Rhodes College (США), у которого есть CubeSat RHOK-SAT
 • По данным поиска, студенты SANSA обучаются в Rhodes по MSc Space Science (страница research.sansa.org.za недоступна — не подтверждено)
-• Международный офис: тел. +27 46 603 8217; адрес Eden Grove Building, Lucas Avenue, Makhanda 6139</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
+• Международный офис: тел. +27 46 603 8217; адрес Eden Grove Building, Lucas Avenue, Makhanda 6139
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ru.ac.za/contactus/
 • Https://www.ru.ac.za/internationalisation/contactus/
 • Https://www.ru.ac.za/vice-chancellor/
 • Https://www.ru.ac.za/latestnews/open_day_2026.html
 • Https://businesstech.co.za/news/lifestyle/864277/south-africa-has-a-new-number-one-university-in-gauteng-second-only-to-uct-nationally/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4088,30 +4361,196 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
+          <t>Претория</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>University of South Africa</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>University of South Africa</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Классический</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Государственный (публичный университет, DHET)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>• Distance education
+• Economic and Management Sciences
+• Education
+• Human Sciences
+• Law
+• Science
+• Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>intpartners@unisa.ac.za</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Dr Angeline Magabane
+Директор по интернационализации и партнёрствам
+Управление интернационализации и партнёрств (Internationalisation &amp; Partnerships)
+Обращение: Dear Dr Magabane,</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>intpartners@unisa.ac.za</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>enquire@unisa.ac.za</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.unisa.ac.za</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Puleng LenkaBula</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>Vice-Chancellor</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 951–1000</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: 1201–1400</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4" t="inlineStr"/>
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
+          <t>• Крупнейший в Африке университет дистанционного обучения
+• Ректор LenkaBula переназначена на второй срок с 1.01.2026; вокруг неё были обвинения группы «Save Unisa» — проверить перед отправкой
+• Почтовый адрес и общий телефон на проверенных страницах не найдены — оставлены пустыми
+• Директор по интернационализации Dr Angeline Magabane (magabm@unisa.ac.za), подтверждено IEASA 2025
+• Быстрая проверка: запущенных спутников не найдено
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>• Https://www.unisa.ac.za/sites/corporate/default/About/Governance-&amp;-management/Executive-management
+• Https://www.unisa.ac.za/sites/corporate/default/About/Internationalisation/Contact-us
+• Https://www.unisa.ac.za/sites/corporate/default/Contact-us
+• Https://thestar.co.za/news/2026-02-12-unisa-charts-decisive-path-for-2026-as-vc-lenkabula-links-global-turbulence-to-local-action/
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AK15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ЮАР</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
           <t>Кейптаун</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>University of the Western Cape</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>University of the Western Cape</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Классический</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Государственный (публичный университет, DHET)</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>• Natural Sciences
 • Community and Health Sciences
@@ -4121,17 +4560,17 @@
 • Education</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>University of the Western Cape, Robert Sobukwe Road, Bellville 7535, South Africa</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>trsingh@uwc.ac.za</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Dr Tasmeera Singh
 Директор по международным связям и SANORD
@@ -4139,132 +4578,149 @@
 Обращение: Dear Dr Singh,</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>личный, совпало</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>trsingh@uwc.ac.za</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>info@uwc.ac.za</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+27 21 959 2911</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>https://www.uwc.ac.za</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>Prof. Robert John Balfour</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>Rector and Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 1001–1200</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr"/>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="n">
+      <c r="X16" s="4" t="inlineStr"/>
+      <c r="Y16" s="4" t="inlineStr"/>
+      <c r="Z16" s="4" t="inlineStr"/>
+      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD15" s="7" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>• Ректор Balfour в должности с 1.01.2025 (в UWC должность называется Rector and Vice-Chancellor)
 • Офис международных связей (IRO) также ведёт секретариат SANORD; общий адрес iro@uwc.ac.za встречается в поисковой выдаче, но на официальной странице не подтверждён
 • Быстрая проверка: запущенных спутников не найдено
-• Сайт ограничивает частоту запросов (429)</t>
-        </is>
-      </c>
-      <c r="AH15" s="4" t="inlineStr">
+• Сайт ограничивает частоту запросов (429)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI16" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uwc.ac.za/about/leadership
 • Https://www.uwc.ac.za/about/international-relations/contact
-• Https://www.uwc.ac.za/news-and-announcements/news/watch-meet-the-university-of-the-western-capes-new-rector-and-vice-chancellor-prof-robert-balfour-8315</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr">
+• Https://www.uwc.ac.za/news-and-announcements/news/watch-meet-the-university-of-the-western-capes-new-rector-and-vice-chancellor-prof-robert-balfour-8315
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK16" s="4" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>ЮАР</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Дурбан</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Durban University of Technology</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Durban University of Technology</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Технический / аэрокосмический</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Государственный (публичный университет, DHET)</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>• Engineering and the Built Environment
 • Applied Sciences
@@ -4274,17 +4730,17 @@
 • Arts and Design</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Durban University of Technology, PO Box 1334, Durban 4000, South Africa</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>samuelsl@dut.ac.za</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Dr Lavern Samuels
 Директор офиса международного образования и партнёрств (IEP)
@@ -4292,133 +4748,149 @@
 Обращение: Dear Dr Samuels,</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>личный, совпало</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>samuelsl@dut.ac.za</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>info@dut.ac.za</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+27 31 373 2000</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>https://www.dut.ac.za</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Prof. Thandwa Zizwe Mthembu</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="n">
+      <c r="X17" s="4" t="inlineStr"/>
+      <c r="Y17" s="4" t="inlineStr"/>
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="7" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Университет технологий (UoT), ведущий среди шести UoT ЮАР; спутников не найдено (одна проверка)
 • Офис International Education and Partnerships (IEP): ML Sultan Campus, D Block, 7–8 этаж; тел. директора +27 31 373 5474
-• Prof. Mthembu — ректор с октября 2016 г</t>
-        </is>
-      </c>
-      <c r="AH16" s="4" t="inlineStr">
+• Prof. Mthembu — ректор с октября 2016 г
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.dut.ac.za/contact/
 • Https://www.dut.ac.za/international_education_and_partnerships/
 • Https://www.dut.ac.za/senior_management_team/prof-mthembu/
 • Https://www.dut.ac.za/vice-chancellor/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ16" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>ЮАР</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Гкеберха (Порт-Элизабет)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Nelson Mandela University</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Nelson Mandela University</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Классический</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Государственный (публичный университет, DHET)</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>• Engineering
 • The Built Environment and Technology
@@ -4429,17 +4901,17 @@
 • Humanities</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>PO Box 77000, Nelson Mandela University, Gqeberha 6031, South Africa</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>international@mandela.ac.za</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Prof. Judy Peter
 Старший директор Международного офиса
@@ -4447,134 +4919,151 @@
 Обращение: Dear Prof. Peter,</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>international@mandela.ac.za</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>info@mandela.ac.za</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+27 41 504 1111</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>https://www.mandela.ac.za</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Prof. Sibongile Muthwa</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr">
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 1401+</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="n">
+      <c r="X18" s="4" t="inlineStr"/>
+      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="Z18" s="4" t="inlineStr"/>
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
+      <c r="AE18" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Второй срок ректора Muthwa начался 30.03.2022
 • International Office: старший директор Prof Judy Peter (IEASA 2025), личный e-mail Judy.Peter@mandela.ac.za
 • Университет (тогда NMMU) поставил научный эксперимент на борт SumbandilaSat (2009) — это полезная нагрузка, а не собственный спутник
-• Адрес international@mandela.ac.za на сайте указан для запросов по учёбе за рубежом</t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
+• Адрес international@mandela.ac.za на сайте указан для запросов по учёбе за рубежом
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI18" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mandela.ac.za/Leadership-and-Governance
 • Https://www.mandela.ac.za/Research,-Innovation-and-Internationalisation
 • Https://international.mandela.ac.za
 • Https://ieasa.studysa.org/about-us/directors-forum/
-• Https://www.universityworldnews.com/post.php?story=20090918125617455</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr">
+• Https://www.universityworldnews.com/post.php?story=20090918125617455
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK18" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>ЮАР</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Претория (Га-Ранкува)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sefako Makgatho Health Sciences University</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Sefako Makgatho Health Sciences University</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Медицинский</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Государственный (публичный университет, DHET)</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>• Medicine
 • Dentistry
@@ -4583,17 +5072,17 @@
 • Science and Technology</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Sefako Makgatho Health Sciences University, Registry, PO Box 60, Medunsa 0204, South Africa; physical: Molotlegi Street, Ga-Rankuwa, Pretoria, Gauteng</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>carlien.jooste@smu.ac.za</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Dr Carlien Jooste
 Директор по интернационализации (Director: Internationalisation)
@@ -4601,131 +5090,146 @@
 Обращение: Dear Dr Jooste,</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>личный, совпало</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>carlien.jooste@smu.ac.za</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+27 12 521 5759</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>https://www.smu.ac.za</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Prof. Dini Mawela</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>Acting Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="4" t="inlineStr"/>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="n">
+      <c r="X19" s="4" t="inlineStr"/>
+      <c r="Y19" s="4" t="inlineStr"/>
+      <c r="Z19" s="4" t="inlineStr"/>
+      <c r="AA19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD18" s="7" t="inlineStr">
+      <c r="AE19" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Медицинский университет — профиль слабо соответствует CubeSat-проекту; спутников не найдено
 • Ректор Prof. Tandi Matsha-Erasmus скончалась в июне 2026 г.; обязанности ректора исполняет Prof. Dini Mawela (Acting Vice-Chancellor) — учесть деликатность в письме
 • Общий email не опубликован (на сайте только форма обратной связи); телефон — регистратура (012) 521 5759
-• Международное направление курирует и. о. DVC Prof. Douglas Maleka (Research, Innovation and Internationalisation)</t>
-        </is>
-      </c>
-      <c r="AH18" s="4" t="inlineStr">
+• Международное направление курирует и. о. DVC Prof. Douglas Maleka (Research, Innovation and Internationalisation)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI19" s="4" t="inlineStr">
         <is>
           <t>• Https://www.smu.ac.za/contacts/
 • Https://www.smu.ac.za/explore-smu/who-we-are/executive-management/
 • Https://www.smu.ac.za/explore-smu/departments/institutional-advancement-and-internationalisation/
 • Https://ieasa.studysa.org/about-us/directors-forum/
 • Https://www.dut.ac.za/
-• Https://www.timeslive.co.za/news/south-africa/2026-06-18-smu-vice-chancellor-tandi-matsha-erasmus-has-died/</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr">
+• Https://www.timeslive.co.za/news/south-africa/2026-06-18-smu-vice-chancellor-tandi-matsha-erasmus-has-died/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ18" s="4" t="inlineStr"/>
+      <c r="AK19" s="4" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>ЮАР</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Претория</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Tshwane University of Technology</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Tshwane University of Technology</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Технический / аэрокосмический</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Государственный (публичный университет, DHET)</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>• Engineering and the Built Environment
 • Information and Communication Technology
@@ -4735,17 +5239,17 @@
 • Arts and Design</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Tshwane University of Technology, Staatsartillerie Road, Pretoria West, Pretoria 0183, South Africa (physical address of Internationalisation Office, Building 4-236; postal box not verified)</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Internationalisation@tut.ac.za</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Mr Caiphus Motadi
 Менеджер офиса интернационализации (Manager: Internationalisation)
@@ -4753,247 +5257,113 @@
 Обращение: Dear Mr Motadi,</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>ящик общий</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Internationalisation@tut.ac.za</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>general@tut.ac.za</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+27 86 110 2421</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>https://www.tut.ac.za</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Prof. Tinyiko Maluleke</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="n">
+      <c r="X20" s="4" t="inlineStr"/>
+      <c r="Y20" s="4" t="inlineStr"/>
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD19" s="7" t="inlineStr">
+      <c r="AE20" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Спутников TUT в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки (F'SATI исторически имеет узел в TUT — не проверено)
 • Есть два международных подразделения: Internationalisation Office (партнёрства, Research &amp; Innovation; менеджер Mr Caiphus Motadi, +27 12 382 4731) и International Students Office (internationaloffice@tut.ac.za, студенты)
-• Офис ректора: Elizma van der Linde, +27 12 382 4112, VanDerLindeME@tut.ac.za; в IEASA (2025) TUT представляет Dr Rita Raseleka, Director: Research &amp; Innovation (raselekarm@tut.ac.za)</t>
-        </is>
-      </c>
-      <c r="AH19" s="4" t="inlineStr">
+• Офис ректора: Elizma van der Linde, +27 12 382 4112, VanDerLindeME@tut.ac.za; в IEASA (2025) TUT представляет Dr Rita Raseleka, Director: Research &amp; Innovation (raselekarm@tut.ac.za)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tut.ac.za/contact-us
 • Https://www.tut.ac.za/about/executive-management-committee/
 • Https://www.tut.ac.za/research--innovation/internationalisation/
 • Https://www.tut.ac.za/international-office/international-office-contacts/
 • Https://ieasa.studysa.org/about-us/directors-forum/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ЮАР</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Претория</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>University of South Africa</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>University of South Africa</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Классический</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Государственный (публичный университет, DHET)</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>• Distance education
-• Economic and Management Sciences
-• Education
-• Human Sciences
-• Law
-• Science
-• Engineering and Technology</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>intpartners@unisa.ac.za</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Dr Angeline Magabane
-Директор по интернационализации и партнёрствам
-Управление интернационализации и партнёрств (Internationalisation &amp; Partnerships)
-Обращение: Dear Dr Magabane,</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>ящик общий</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>intpartners@unisa.ac.za</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>enquire@unisa.ac.za</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.unisa.ac.za</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>Prof. Puleng LenkaBula</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t>Vice-Chancellor</t>
-        </is>
-      </c>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>THE2027: 1201–1400</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="inlineStr"/>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD20" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE20" s="4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="AF20" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="inlineStr">
-        <is>
-          <t>• Крупнейший в Африке университет дистанционного обучения
-• Ректор LenkaBula переназначена на второй срок с 1.01.2026; вокруг неё были обвинения группы «Save Unisa» — проверить перед отправкой
-• Почтовый адрес и общий телефон на проверенных страницах не найдены — оставлены пустыми
-• Директор по интернационализации Dr Angeline Magabane (magabm@unisa.ac.za), подтверждено IEASA 2025
-• Быстрая проверка: запущенных спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH20" s="4" t="inlineStr">
-        <is>
-          <t>• Https://www.unisa.ac.za/sites/corporate/default/About/Governance-&amp;-management/Executive-management
-• Https://www.unisa.ac.za/sites/corporate/default/About/Internationalisation/Contact-us
-• Https://www.unisa.ac.za/sites/corporate/default/Contact-us
-• Https://thestar.co.za/news/2026-02-12-unisa-charts-decisive-path-for-2026-as-vc-lenkabula-links-global-turbulence-to-local-action/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AJ20" s="4" t="inlineStr"/>
+      <c r="AK20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -5089,63 +5459,78 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
       <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="n">
+      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD21" s="7" t="inlineStr">
+      <c r="AE21" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• Сайт univen.ac.za напрямую из нашей сети недоступен (ошибка TLS через прокси); страницы открыты через r.jina.ai 04.10.2026
 • Dr Olusegun Obadire — Director: International Relations and Partnerships (страница Director’s Profile). Личный e-mail директора (segun.obadire@univen.ac.za, из IEASA 2025) на сайте не опубликован — заменён на общий international.students@univen.ac.za
 • По вопросам научного сотрудничества и институциональных партнёрств сайт IRP указывает matome.mokoena@univen.ac.za; мобильность/Erasmus+ — nontlanhla.ntakana@univen.ac.za; WhatsApp IRP +27 60 677 0033
 • Быстрая проверка: спутников не найдено
-• Перепроверка: Сайт univen.ac.za открыт через reader-сервис 04.10.2026: VC Prof Bernard Nthambeleni, директор IRP Dr Olusegun Obadire (уже не «и.о.»), общий e-mail и телефоны IRP, адрес Private Bag X5050 подтверждены; e-mail international заменён на официальный общий ящик IRP</t>
-        </is>
-      </c>
-      <c r="AH21" s="4" t="inlineStr">
+• Перепроверка: Сайт univen.ac.za открыт через reader-сервис 04.10.2026: VC Prof Bernard Nthambeleni, директор IRP Dr Olusegun Obadire (уже не «и.о.»), общий e-mail и телефоны IRP, адрес Private Bag X5050 подтверждены; e-mail international заменён на официальный общий ящик IRP
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.univen.ac.za/news/univen-opens-2026-academic-year-with-a-renewed-commitment-to-excellence-impact-and-student-success/
 • Https://www.univen.ac.za/contact-us/
 • Https://www.univen.ac.za/irp/study-at-univen/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ21" s="4" t="inlineStr"/>
+      <c r="AK21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5246,7 +5631,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 1001-1200</t>
+          <t>QS2027: 1001–1200</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr">
@@ -5254,57 +5639,70 @@
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
       <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="n">
+      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD22" s="7" t="inlineStr">
+      <c r="AE22" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Prof. Hester Klopper — ректор с 1 февраля 2025 г., первая женщина на этом посту
 • Международное направление курирует DVC: Strategic Initiatives, International and Institutional Affairs Prof. Sam Tshehla (с 1 апреля 2026)
 • Prof. Lynette Jacobs указана как исполняющая обязанности директора Office for International Affairs (данные IEASA за 2025 г.); с 2026 г. подразделение называется Directorate for International Partnerships and Relations — должность директора стоит перепроверить
-• Спутников не найдено (одна проверка)</t>
-        </is>
-      </c>
-      <c r="AH22" s="4" t="inlineStr">
+• Спутников не найдено (одна проверка)
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ufs.ac.za/contact-us
 • Https://www.ufs.ac.za/international
 • Https://www.ufs.ac.za/about-the-ufs/governance/rectorate
 • Https://ieasa.studysa.org/about-us/directors-forum/
-• Https://businesstech.co.za/news/lifestyle/864277/south-africa-has-a-new-number-one-university-in-gauteng-second-only-to-uct-nationally/</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="inlineStr">
+• Https://businesstech.co.za/news/lifestyle/864277/south-africa-has-a-new-number-one-university-in-gauteng-second-only-to-uct-nationally/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ22" s="4" t="inlineStr"/>
+      <c r="AK22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -5401,62 +5799,77 @@
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="S23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
       <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="n">
+      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD23" s="7" t="inlineStr">
+      <c r="AE23" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Отдельного общего email нет; vutmedia@vut.ac.za — ящик, привязанный к блоку General Enquiries / медиа на странице контактов
 • Директор International Office Mr Vido Kungune: тел. 016 950 9377, офис A009-18 (подтверждено также IEASA 2025)
-• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки</t>
-        </is>
-      </c>
-      <c r="AH23" s="4" t="inlineStr">
+• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI23" s="4" t="inlineStr">
         <is>
           <t>• Https://www.vut.ac.za/contact-us/
 • Https://www.vut.ac.za/international-office/
 • Https://www.vut.ac.za/executive-management/
 • Https://ieasa.studysa.org/about-us/directors-forum/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -5552,61 +5965,76 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
       <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="n">
+      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD24" s="7" t="inlineStr">
+      <c r="AE24" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• Во входном списке указано как «iYunivesithi Walter Sisulu» — это официальное брендовое название; английское — Walter Sisulu University
 • Директор по интернационализации и партнёрствам — Dr Mzolisi Payi (отдельный e-mail не опубликован); рекомендуется адресовать письмо ему через enquiries@wsu.ac.za
 • Кампусы: Мтата, Баттерворт, Ист-Лондон (Buffalo City), Комани
-• Быстрая проверка: спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH24" s="4" t="inlineStr">
+• Быстрая проверка: спутников не найдено
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI24" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wsu.ac.za/en/home-wsu/governance-leadership-wsu/leadership
 • Https://www.wsu.ac.za/en/contact-us
-• Https://www.wsu.ac.za/en/internationalisation-partnerships-directorate</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="inlineStr">
+• Https://www.wsu.ac.za/en/internationalisation-partnerships-directorate
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -5695,56 +6123,74 @@
           <t>Executive Director</t>
         </is>
       </c>
-      <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="n">
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="n">
+      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="7" t="inlineStr">
+      <c r="AE25" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Некоммерческий институт (часть панафриканской сети AIMS), а не университет — ownership «Частный» условно
 • Учёное звание руководителя на сайте не указано — в обращении не использовать «Prof.» без проверки
 • Телефон на официальной странице не опубликован
-• Спутниковой деятельности нет; интерес — AI/данные для обработки спутниковых данных</t>
-        </is>
-      </c>
-      <c r="AH25" s="4" t="inlineStr">
+• Спутниковой деятельности нет; интерес — AI/данные для обработки спутниковых данных
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI25" s="4" t="inlineStr">
         <is>
           <t>• Https://aims.ac.za/contact/
 • Https://aims.ac.za/team/</t>
         </is>
       </c>
-      <c r="AI25" s="4" t="inlineStr">
+      <c r="AJ25" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
+      <c r="AK25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -5838,45 +6284,63 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="n">
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
       <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="n">
+      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="7" t="inlineStr">
+      <c r="AE26" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• Университет технологий; общего e-mail нет (только портал Ask CUT)
 • Centre for Global Engagement (CGE): старший директор Valindawo Dwayi (учёное звание/обращение не указано)
 • Profile_type указан как technical/aerospace по типу вуза (University of Technology); аэрокосмических подразделений не найдено
-• Быстрая проверка: спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH26" s="4" t="inlineStr">
+• Быстрая проверка: спутников не найдено
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI26" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cut.ac.za/
 • Https://www.cut.ac.za/management
@@ -5884,12 +6348,12 @@
 • Https://www.cut.ac.za/contact-details-by-category</t>
         </is>
       </c>
-      <c r="AI26" s="4" t="inlineStr">
+      <c r="AJ26" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ26" s="4" t="inlineStr"/>
+      <c r="AK26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -5983,56 +6447,74 @@
           <t>Campus Head (Ruimsig Johannesburg)</t>
         </is>
       </c>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="n">
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
       <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="n">
+      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="7" t="inlineStr">
+      <c r="AE27" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• IIE MSA (бывший Monash South Africa) больше не существует как отдельный бренд: сайт iiemsa.co.za перенаправляет на Emeris — объединённый бренд IIE (Varsity College, IIE MSA, Vega, School of Hospitality); частный вуз, регистрация DHET 2007/HE07/002
 • Нет ректора/вице-канцлера и международного офиса на уровне кампуса; указан руководитель кампуса Ruimsig (учёное звание не указано); ruimsig@emeris.ac.za — общий ящик кампуса
-• Частный вуз без инженерно-космического профиля; спутников нет; низкий приоритет для CubeSat-группировки</t>
-        </is>
-      </c>
-      <c r="AH27" s="4" t="inlineStr">
+• Частный вуз без инженерно-космического профиля; спутников нет; низкий приоритет для CubeSat-группировки
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI27" s="4" t="inlineStr">
         <is>
           <t>• Https://www.emeris.ac.za/campuses/ruimsig-johannesburg
 • Https://www.emeris.ac.za/about
 • Https://www.iiemsa.co.za/ (redirects to emeris.ac.za)</t>
         </is>
       </c>
-      <c r="AI27" s="4" t="inlineStr">
+      <c r="AJ27" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ27" s="4" t="inlineStr"/>
+      <c r="AK27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6126,44 +6608,62 @@
           <t>Interim Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="n">
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
       <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="n">
+      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AD28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="7" t="inlineStr">
+      <c r="AE28" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Отдельного международного офиса/email нет: интернационализация находится в директорате Marketing and Communications под кураторством ректора; ведущее лицо — Senior Director: Marketing and Communication (на сайте указан как «M Mkhize», учёное звание не указано)
 • Ректор — временный (Interim VC) Prof. Rushiella Songca; офис ректора: тел. 031 907 7219, adsecretary@mut.ac.za
-• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки</t>
-        </is>
-      </c>
-      <c r="AH28" s="4" t="inlineStr">
+• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mut.ac.za/contact-us/
 • Https://www.mut.ac.za/about-mut/leadership-and-governance/
@@ -6171,12 +6671,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI28" s="4" t="inlineStr">
+      <c r="AJ28" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ28" s="4" t="inlineStr"/>
+      <c r="AK28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6271,57 +6771,75 @@
           <t>Chief Executive Officer (CEO) - Principal</t>
         </is>
       </c>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="n">
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
       <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="n">
+      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AD29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="7" t="inlineStr">
+      <c r="AE29" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>• Частный вуз (STADIO (Pty) Ltd, регистрация DHET 2008/HE07/004), в основном дистанционное обучение
 • Hello@stadio.ac.za — адрес поддержки абитуриентов (единственный опубликованный)
 • Адрес головного офиса — со страницы STADIO Holdings
-• Космической деятельности нет — низкий приоритет для приглашения</t>
-        </is>
-      </c>
-      <c r="AH29" s="4" t="inlineStr">
+• Космической деятельности нет — низкий приоритет для приглашения
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI29" s="4" t="inlineStr">
         <is>
           <t>• Https://www.stadio.ac.za/about-stadio/leadership
 • Https://www.stadio.ac.za/contact-us
 • Https://stadio.co.za/contact-us/</t>
         </is>
       </c>
-      <c r="AI29" s="4" t="inlineStr">
+      <c r="AJ29" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ29" s="4" t="inlineStr"/>
+      <c r="AK29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6413,46 +6931,64 @@
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="n">
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
       <c r="AB30" s="4" t="inlineStr"/>
-      <c r="AC30" s="4" t="n">
+      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AD30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="7" t="inlineStr">
+      <c r="AE30" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• Общий email и международный офис на сайте не опубликованы; studentrecruitment@spu.ac.za — ящик набора студентов (единственный общий адрес) — лучше звонить на коммутатор +27 53 491 0000 и запросить адрес офиса ректора
 • Молодой университет (осн. 2014) в Кимберли; для исследовательского партнёрства релевантен DVC: Research, Innovation and Postgraduate Affairs Prof. Jose Frantz
 • Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки
 • 04.10.2026 на сайте подтверждены: VC Prof. Debra Meyer (Executive Management), коммутатор +27 53 491 0000 и адрес Central Campus (страница Contact); общего e-mail и международного офиса на сайте по-прежнему нет
-• Перепроверка: Ректор, телефон и адрес подтверждены на сайте spu.ac.za 04.10.2026; общий e-mail/международный офис не опубликованы</t>
-        </is>
-      </c>
-      <c r="AH30" s="4" t="inlineStr">
+• Перепроверка: Ректор, телефон и адрес подтверждены на сайте spu.ac.za 04.10.2026; общий e-mail/международный офис не опубликованы
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.spu.ac.za/index.php/contact-spu/
 • Https://www.spu.ac.za/index.php/leadership-and-governance/
@@ -6460,12 +6996,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI30" s="4" t="inlineStr">
+      <c r="AJ30" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ30" s="4" t="inlineStr"/>
+      <c r="AK30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6564,57 +7100,75 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="n">
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
       <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="n">
+      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AD31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD31" s="7" t="inlineStr">
+      <c r="AE31" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Указан физический адрес кампуса Элис (почтовый ящик на проверенной странице не найден)
 • Директор IAP Mr Lebethe Malefo, личный e-mail LMalefo@ufh.ac.za, тел. +27 43 704 7666; менеджер по партнёрствам Ms Quinter Onyango (QOnyango@ufh.ac.za)
 • Исторический университет (выпускники — Нельсон Мандела и др.)
-• Быстрая проверка: спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH31" s="4" t="inlineStr">
+• Быстрая проверка: спутников не найдено
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI31" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ufh.ac.za/about-us
 • Https://www.ufh.ac.za/international-affairs-and-partnerships
 • Https://www.ufh.ac.za/international-affairs-and-partnerships/about-iap</t>
         </is>
       </c>
-      <c r="AI31" s="4" t="inlineStr">
+      <c r="AJ31" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ31" s="4" t="inlineStr"/>
+      <c r="AK31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -6711,45 +7265,63 @@
           <t>Vice-Chancellor and Principal</t>
         </is>
       </c>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="n">
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
       <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="n">
+      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AD32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD32" s="7" t="inlineStr">
+      <c r="AE32" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Общего email нет — enrolment@ul.ac.za (приём/общие контакты, +27 15 268 3332) указан на сайте как «General contacts»
 • Ректор Dr Jeffrey Mabelebele — назван на сайте «новым» ректором; учёное звание — Dr (не Prof.)
 • Директор Office of International Affairs — Prof. Nonceba Mbambo-Kekana по данным IEASA (2025); на сайте UL имя не найдено — перепроверить
-• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки</t>
-        </is>
-      </c>
-      <c r="AH32" s="4" t="inlineStr">
+• Спутников в nanosats.csv не найдено; квота веб-поиска исчерпана до отдельной проверки
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI32" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ul.ac.za/contact-us/
 • Https://www.ul.ac.za/about-us/
@@ -6759,12 +7331,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI32" s="4" t="inlineStr">
+      <c r="AJ32" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ32" s="4" t="inlineStr"/>
+      <c r="AK32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -6858,55 +7430,73 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="n">
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
       <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="n">
+      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AD33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" s="7" t="inlineStr">
+      <c r="AE33" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Молодой университет (основан в 2014 г.), сильный аграрный профиль
 • Директор International Partnerships &amp; Networks — Mr Thabo Dikgale (с 1.03.2026), e-mail не опубликован; рекомендуется адресовать письмо ему через info@ump.ac.za
-• Быстрая проверка: спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH33" s="4" t="inlineStr">
+• Быстрая проверка: спутников не найдено
+• Рейтинги: Национального рейтинга нет: DHET и CHE вузы не ранжируют</t>
+        </is>
+      </c>
+      <c r="AI33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ump.ac.za/
 • Https://www.ump.ac.za/Research-and-Innovation/Partnerships-(1).aspx</t>
         </is>
       </c>
-      <c r="AI33" s="4" t="inlineStr">
+      <c r="AJ33" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ33" s="4" t="inlineStr"/>
+      <c r="AK33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -6964,9 +7554,10 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Prof. Nokuthula Kunene
+Vice-Chancellor
 Приёмная комиссия (Admissions)
-Обращение: Dear Director of the International Office,</t>
+Обращение: Dear Prof. Kunene,</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -7000,37 +7591,46 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr"/>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="n">
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
       <c r="AB34" s="4" t="inlineStr"/>
-      <c r="AC34" s="4" t="n">
+      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AD34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD34" s="7" t="inlineStr">
+      <c r="AE34" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF34" s="4" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
       <c r="AG34" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Сайт unizulu.ac.za недоступен (503/таймаут) — данные из поисковой выдачи
 • Prof Kunene назначена ректором с 2026 г. (Prof Mtose оставалась до 31.03.2026) — проверить вступление в должность
@@ -7038,26 +7638,29 @@
 • Международный офис и его руководитель не установлены; в IEASA 2025 университет представляла Prof Nontokozo Mashiya (Director: VC's Office, MashiyaN@unizulu.ac.za)
 • Быстрая проверка: спутников не найдено
 • Повторная проверка 04.10.2026: официальных страниц международного офиса найти не удалось
-• Перепроверка: Сайт unizulu.ac.za недоступен по HTTPS, по HTTP — заглушка обновления LMS; данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH34" s="4" t="inlineStr">
+• Перепроверка: Сайт unizulu.ac.za недоступен по HTTPS, по HTTP — заглушка обновления LMS; данные не изменены
+• Ручная проверка: Контакты прочитаны на официальном сайте 05.10.2026 (сессия с агентами). Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI34" s="4" t="inlineStr">
         <is>
           <t>• Https://witness.co.za/news/2025/09/18/unizulu-appoints-professor-kunene-as-its-new-vice-chancellor/
 • Https://usaf.ac.za/universities-south-africa-welcomes-a-new-cohort-of-vice-chancellors-in-2026/
 • Https://www.unizulu.ac.za/contact-us/
-• Https://ieasa.studysa.org/about-us/directors-forum/</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr">
+• Https://ieasa.studysa.org/about-us/directors-forum/
+https://www.unizulu.ac.za/executive-management/
+• Https://www.unizulu.ac.za/contact-us/</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ34" s="4" t="inlineStr"/>
+      <c r="AK34" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ34"/>
+  <autoFilter ref="A1:AK34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>